--- a/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Servlet/MainServlet_クラス仕様書.xlsx
+++ b/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Servlet/MainServlet_クラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5C8F2A-B3EE-434A-A315-69C2AB662410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D145E875-C52E-4286-AA15-683A13EA296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="メソッド仕様（doPost）" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（doGet）'!$A$1:$BI$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（doGet）'!$A$1:$BI$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'メソッド仕様（doPost）'!$A$1:$BI$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="85">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -296,22 +296,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>2.1　変数宣言：[session] ログイン情報を持つセッションを取得</t>
-    <rPh sb="4" eb="8">
-      <t>ヘンスウセンゲン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>3.1 変数宣言：[cas] CheckAccessServiceクラスをインスタンス化し、代入</t>
     <rPh sb="4" eb="8">
       <t>ヘンスウセンゲン</t>
@@ -342,16 +326,6 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>ヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>3.3 CheckAccessServiceのcheckLoginメソッドの呼出</t>
-    <rPh sb="38" eb="39">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ダ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -498,6 +472,26 @@
       <t>ゾクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.1　変数宣言：[session] セッションを取得</t>
+    <rPh sb="4" eb="8">
+      <t>ヘンスウセンゲン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>3.3 CheckAccessServiceのgetSessionFlgメソッドの呼出</t>
+    <rPh sb="41" eb="42">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -2732,7 +2726,7 @@
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B17" s="54"/>
       <c r="C17" s="54"/>
@@ -3185,7 +3179,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX37"/>
+  <dimension ref="A1:IX36"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
@@ -5607,7 +5601,7 @@
       <c r="B11" s="74"/>
       <c r="C11" s="74"/>
       <c r="D11" s="63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="63"/>
       <c r="F11" s="63"/>
@@ -5621,7 +5615,7 @@
       <c r="N11" s="63"/>
       <c r="O11" s="63"/>
       <c r="P11" s="63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="63"/>
       <c r="R11" s="63"/>
@@ -5638,7 +5632,7 @@
       <c r="AC11" s="63"/>
       <c r="AD11" s="63"/>
       <c r="AE11" s="63" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF11" s="63"/>
       <c r="AG11" s="63"/>
@@ -5875,7 +5869,7 @@
       <c r="B12" s="74"/>
       <c r="C12" s="74"/>
       <c r="D12" s="63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="63"/>
       <c r="F12" s="63"/>
@@ -5889,7 +5883,7 @@
       <c r="N12" s="63"/>
       <c r="O12" s="63"/>
       <c r="P12" s="63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="63"/>
@@ -5906,7 +5900,7 @@
       <c r="AC12" s="63"/>
       <c r="AD12" s="63"/>
       <c r="AE12" s="63" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF12" s="63"/>
       <c r="AG12" s="63"/>
@@ -6143,7 +6137,7 @@
       <c r="B13" s="74"/>
       <c r="C13" s="74"/>
       <c r="D13" s="63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="63"/>
       <c r="F13" s="63"/>
@@ -6157,7 +6151,7 @@
       <c r="N13" s="63"/>
       <c r="O13" s="63"/>
       <c r="P13" s="63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q13" s="63"/>
       <c r="R13" s="63"/>
@@ -6174,7 +6168,7 @@
       <c r="AC13" s="63"/>
       <c r="AD13" s="63"/>
       <c r="AE13" s="63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF13" s="63"/>
       <c r="AG13" s="63"/>
@@ -8254,7 +8248,7 @@
       <c r="Q21" s="45"/>
       <c r="R21" s="43"/>
       <c r="S21" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="22"/>
@@ -8485,13 +8479,39 @@
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="50" t="s">
-        <v>53</v>
+      <c r="O22" s="51" t="s">
+        <v>54</v>
       </c>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="43"/>
-      <c r="T22" s="21"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
+      <c r="AE22" s="36"/>
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="36"/>
+      <c r="AH22" s="36"/>
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="36"/>
+      <c r="AK22" s="36"/>
+      <c r="AL22" s="36"/>
+      <c r="AM22" s="36"/>
+      <c r="AN22" s="36"/>
+      <c r="AO22" s="36"/>
+      <c r="AP22" s="36"/>
+      <c r="AQ22" s="36"/>
+      <c r="AR22" s="36"/>
+      <c r="AS22" s="53"/>
       <c r="AT22" s="7"/>
       <c r="AU22" s="22"/>
       <c r="AV22" s="22"/>
@@ -8708,8 +8728,7 @@
     </row>
     <row r="23" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="8"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -8721,43 +8740,45 @@
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="51" t="s">
-        <v>54</v>
+      <c r="O23" s="49">
+        <v>3</v>
       </c>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="52"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="36"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="36"/>
-      <c r="Y23" s="36"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="36"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="36"/>
-      <c r="AD23" s="36"/>
-      <c r="AE23" s="36"/>
-      <c r="AF23" s="36"/>
-      <c r="AG23" s="36"/>
-      <c r="AH23" s="36"/>
-      <c r="AI23" s="36"/>
-      <c r="AJ23" s="36"/>
-      <c r="AK23" s="36"/>
-      <c r="AL23" s="36"/>
-      <c r="AM23" s="36"/>
-      <c r="AN23" s="36"/>
-      <c r="AO23" s="36"/>
-      <c r="AP23" s="36"/>
-      <c r="AQ23" s="36"/>
-      <c r="AR23" s="36"/>
-      <c r="AS23" s="53"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T23" s="21"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="12"/>
+      <c r="AE23" s="12"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
       <c r="AT23" s="7"/>
       <c r="AU23" s="22"/>
       <c r="AV23" s="22"/>
-      <c r="AW23" s="9"/>
+      <c r="AW23" s="8"/>
       <c r="AX23" s="9"/>
       <c r="AY23" s="9"/>
       <c r="AZ23" s="9"/>
@@ -8982,16 +9003,15 @@
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="49">
-        <v>3</v>
+      <c r="O24" s="50" t="s">
+        <v>53</v>
       </c>
       <c r="P24" s="45"/>
       <c r="Q24" s="45"/>
       <c r="R24" s="43"/>
-      <c r="S24" s="2" t="s">
-        <v>62</v>
+      <c r="T24" s="21" t="s">
+        <v>47</v>
       </c>
-      <c r="T24" s="21"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
@@ -9233,7 +9253,8 @@
     </row>
     <row r="25" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -9246,14 +9267,15 @@
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="50" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="P25" s="45"/>
       <c r="Q25" s="45"/>
       <c r="R25" s="43"/>
-      <c r="T25" s="21" t="s">
-        <v>47</v>
+      <c r="S25" s="2" t="s">
+        <v>64</v>
       </c>
+      <c r="T25" s="21"/>
       <c r="U25" s="12"/>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
@@ -9509,13 +9531,13 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P26" s="45"/>
       <c r="Q26" s="45"/>
       <c r="R26" s="43"/>
       <c r="S26" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="T26" s="21"/>
       <c r="U26" s="12"/>
@@ -9772,41 +9794,39 @@
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="50" t="s">
-        <v>69</v>
+      <c r="O27" s="51"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="37" t="s">
+        <v>65</v>
       </c>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T27" s="21"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
-      <c r="AC27" s="12"/>
-      <c r="AD27" s="12"/>
-      <c r="AE27" s="12"/>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="12"/>
-      <c r="AI27" s="12"/>
-      <c r="AJ27" s="12"/>
-      <c r="AK27" s="12"/>
-      <c r="AL27" s="12"/>
-      <c r="AM27" s="12"/>
-      <c r="AN27" s="12"/>
-      <c r="AO27" s="12"/>
-      <c r="AP27" s="12"/>
-      <c r="AQ27" s="12"/>
-      <c r="AR27" s="12"/>
-      <c r="AS27" s="12"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="41"/>
+      <c r="AL27" s="41"/>
+      <c r="AM27" s="41"/>
+      <c r="AN27" s="41"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="41"/>
+      <c r="AQ27" s="41"/>
+      <c r="AR27" s="41"/>
+      <c r="AS27" s="42"/>
       <c r="AT27" s="7"/>
       <c r="AU27" s="22"/>
       <c r="AV27" s="22"/>
@@ -10036,39 +10056,41 @@
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="36"/>
-      <c r="T28" s="37" t="s">
-        <v>67</v>
+      <c r="O28" s="49">
+        <v>4</v>
       </c>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="41"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="41"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="41"/>
-      <c r="AK28" s="41"/>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="41"/>
-      <c r="AN28" s="41"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="41"/>
-      <c r="AQ28" s="41"/>
-      <c r="AR28" s="41"/>
-      <c r="AS28" s="42"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AH28" s="13"/>
+      <c r="AI28" s="13"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="13"/>
+      <c r="AM28" s="13"/>
+      <c r="AN28" s="13"/>
+      <c r="AO28" s="13"/>
+      <c r="AP28" s="13"/>
+      <c r="AQ28" s="13"/>
+      <c r="AR28" s="13"/>
+      <c r="AS28" s="13"/>
       <c r="AT28" s="7"/>
       <c r="AU28" s="22"/>
       <c r="AV28" s="22"/>
@@ -10298,42 +10320,44 @@
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="49">
-        <v>4</v>
+      <c r="O29" s="51" t="s">
+        <v>72</v>
       </c>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="13" t="s">
-        <v>78</v>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="38" t="s">
+        <v>77</v>
       </c>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
-      <c r="AH29" s="13"/>
-      <c r="AI29" s="13"/>
-      <c r="AJ29" s="13"/>
-      <c r="AK29" s="13"/>
-      <c r="AL29" s="13"/>
-      <c r="AM29" s="13"/>
-      <c r="AN29" s="13"/>
-      <c r="AO29" s="13"/>
-      <c r="AP29" s="13"/>
-      <c r="AQ29" s="13"/>
-      <c r="AR29" s="13"/>
-      <c r="AS29" s="13"/>
-      <c r="AT29" s="7"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="38"/>
+      <c r="AA29" s="38"/>
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="38"/>
+      <c r="AD29" s="38"/>
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="38"/>
+      <c r="AG29" s="38"/>
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="38"/>
+      <c r="AJ29" s="38"/>
+      <c r="AK29" s="38"/>
+      <c r="AL29" s="38"/>
+      <c r="AM29" s="38"/>
+      <c r="AN29" s="38"/>
+      <c r="AO29" s="38"/>
+      <c r="AP29" s="38"/>
+      <c r="AQ29" s="38"/>
+      <c r="AR29" s="38"/>
+      <c r="AS29" s="39"/>
+      <c r="AT29" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="AU29" s="22"/>
       <c r="AV29" s="22"/>
       <c r="AW29" s="8"/>
@@ -10562,44 +10586,16 @@
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="51" t="s">
-        <v>74</v>
+      <c r="O30" s="49">
+        <v>5</v>
       </c>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="38" t="s">
-        <v>79</v>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="2" t="s">
+        <v>75</v>
       </c>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="38"/>
-      <c r="Z30" s="38"/>
-      <c r="AA30" s="38"/>
-      <c r="AB30" s="38"/>
-      <c r="AC30" s="38"/>
-      <c r="AD30" s="38"/>
-      <c r="AE30" s="38"/>
-      <c r="AF30" s="38"/>
-      <c r="AG30" s="38"/>
-      <c r="AH30" s="38"/>
-      <c r="AI30" s="38"/>
-      <c r="AJ30" s="38"/>
-      <c r="AK30" s="38"/>
-      <c r="AL30" s="38"/>
-      <c r="AM30" s="38"/>
-      <c r="AN30" s="38"/>
-      <c r="AO30" s="38"/>
-      <c r="AP30" s="38"/>
-      <c r="AQ30" s="38"/>
-      <c r="AR30" s="38"/>
-      <c r="AS30" s="39"/>
-      <c r="AT30" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="AT30" s="7"/>
       <c r="AU30" s="22"/>
       <c r="AV30" s="22"/>
       <c r="AW30" s="8"/>
@@ -10828,15 +10824,39 @@
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="49">
-        <v>5</v>
+      <c r="O31" s="50" t="s">
+        <v>73</v>
       </c>
       <c r="P31" s="46"/>
       <c r="Q31" s="46"/>
       <c r="R31" s="43"/>
-      <c r="S31" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="S31" s="47"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="22"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22"/>
+      <c r="AG31" s="22"/>
+      <c r="AH31" s="22"/>
+      <c r="AI31" s="22"/>
+      <c r="AJ31" s="22"/>
+      <c r="AK31" s="22"/>
+      <c r="AL31" s="22"/>
+      <c r="AM31" s="22"/>
+      <c r="AN31" s="22"/>
+      <c r="AO31" s="22"/>
+      <c r="AP31" s="22"/>
+      <c r="AQ31" s="22"/>
+      <c r="AR31" s="22"/>
+      <c r="AS31" s="48"/>
       <c r="AT31" s="7"/>
       <c r="AU31" s="22"/>
       <c r="AV31" s="22"/>
@@ -11066,39 +11086,39 @@
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="50" t="s">
-        <v>75</v>
+      <c r="O32" s="51" t="s">
+        <v>74</v>
       </c>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="46"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="47"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="22"/>
-      <c r="AC32" s="22"/>
-      <c r="AD32" s="22"/>
-      <c r="AE32" s="22"/>
-      <c r="AF32" s="22"/>
-      <c r="AG32" s="22"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22"/>
-      <c r="AM32" s="22"/>
-      <c r="AN32" s="22"/>
-      <c r="AO32" s="22"/>
-      <c r="AP32" s="22"/>
-      <c r="AQ32" s="22"/>
-      <c r="AR32" s="22"/>
-      <c r="AS32" s="48"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32" s="38"/>
+      <c r="AF32" s="38"/>
+      <c r="AG32" s="38"/>
+      <c r="AH32" s="38"/>
+      <c r="AI32" s="38"/>
+      <c r="AJ32" s="38"/>
+      <c r="AK32" s="38"/>
+      <c r="AL32" s="38"/>
+      <c r="AM32" s="38"/>
+      <c r="AN32" s="38"/>
+      <c r="AO32" s="38"/>
+      <c r="AP32" s="38"/>
+      <c r="AQ32" s="38"/>
+      <c r="AR32" s="38"/>
+      <c r="AS32" s="39"/>
       <c r="AT32" s="7"/>
       <c r="AU32" s="22"/>
       <c r="AV32" s="22"/>
@@ -11328,39 +11348,10 @@
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="38"/>
-      <c r="R33" s="44"/>
-      <c r="S33" s="38"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="38"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="38"/>
-      <c r="X33" s="38"/>
-      <c r="Y33" s="38"/>
-      <c r="Z33" s="38"/>
-      <c r="AA33" s="38"/>
-      <c r="AB33" s="38"/>
-      <c r="AC33" s="38"/>
-      <c r="AD33" s="38"/>
-      <c r="AE33" s="38"/>
-      <c r="AF33" s="38"/>
-      <c r="AG33" s="38"/>
-      <c r="AH33" s="38"/>
-      <c r="AI33" s="38"/>
-      <c r="AJ33" s="38"/>
-      <c r="AK33" s="38"/>
-      <c r="AL33" s="38"/>
-      <c r="AM33" s="38"/>
-      <c r="AN33" s="38"/>
-      <c r="AO33" s="38"/>
-      <c r="AP33" s="38"/>
-      <c r="AQ33" s="38"/>
-      <c r="AR33" s="38"/>
-      <c r="AS33" s="39"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="43"/>
       <c r="AT33" s="7"/>
       <c r="AU33" s="22"/>
       <c r="AV33" s="22"/>
@@ -11809,40 +11800,67 @@
       <c r="IX34" s="1"/>
     </row>
     <row r="35" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
       <c r="O35" s="50"/>
       <c r="P35" s="46"/>
       <c r="Q35" s="46"/>
       <c r="R35" s="43"/>
-      <c r="AT35" s="7"/>
-      <c r="AU35" s="22"/>
-      <c r="AV35" s="22"/>
-      <c r="AW35" s="8"/>
-      <c r="AX35" s="9"/>
-      <c r="AY35" s="9"/>
-      <c r="AZ35" s="9"/>
-      <c r="BA35" s="9"/>
-      <c r="BB35" s="9"/>
-      <c r="BC35" s="9"/>
-      <c r="BD35" s="9"/>
-      <c r="BE35" s="9"/>
-      <c r="BF35" s="9"/>
-      <c r="BG35" s="9"/>
-      <c r="BH35" s="9"/>
-      <c r="BI35" s="10"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="18"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="18"/>
+      <c r="AE35" s="18"/>
+      <c r="AF35" s="18"/>
+      <c r="AG35" s="18"/>
+      <c r="AH35" s="18"/>
+      <c r="AI35" s="18"/>
+      <c r="AJ35" s="18"/>
+      <c r="AK35" s="18"/>
+      <c r="AL35" s="18"/>
+      <c r="AM35" s="18"/>
+      <c r="AN35" s="18"/>
+      <c r="AO35" s="18"/>
+      <c r="AP35" s="18"/>
+      <c r="AQ35" s="18"/>
+      <c r="AR35" s="18"/>
+      <c r="AS35" s="18"/>
+      <c r="AT35" s="14"/>
+      <c r="AU35" s="24"/>
+      <c r="AV35" s="24"/>
+      <c r="AW35" s="15"/>
+      <c r="AX35" s="19"/>
+      <c r="AY35" s="15"/>
+      <c r="AZ35" s="15"/>
+      <c r="BA35" s="15"/>
+      <c r="BB35" s="15"/>
+      <c r="BC35" s="15"/>
+      <c r="BD35" s="15"/>
+      <c r="BE35" s="15"/>
+      <c r="BF35" s="15"/>
+      <c r="BG35" s="15"/>
+      <c r="BH35" s="15"/>
+      <c r="BI35" s="16"/>
       <c r="BJ35" s="1"/>
       <c r="BK35" s="1"/>
       <c r="BL35" s="1"/>
@@ -12042,67 +12060,67 @@
       <c r="IX35" s="1"/>
     </row>
     <row r="36" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="46"/>
-      <c r="Q36" s="46"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18"/>
-      <c r="AB36" s="18"/>
-      <c r="AC36" s="18"/>
-      <c r="AD36" s="18"/>
-      <c r="AE36" s="18"/>
-      <c r="AF36" s="18"/>
-      <c r="AG36" s="18"/>
-      <c r="AH36" s="18"/>
-      <c r="AI36" s="18"/>
-      <c r="AJ36" s="18"/>
-      <c r="AK36" s="18"/>
-      <c r="AL36" s="18"/>
-      <c r="AM36" s="18"/>
-      <c r="AN36" s="18"/>
-      <c r="AO36" s="18"/>
-      <c r="AP36" s="18"/>
-      <c r="AQ36" s="18"/>
-      <c r="AR36" s="18"/>
-      <c r="AS36" s="18"/>
-      <c r="AT36" s="14"/>
-      <c r="AU36" s="24"/>
-      <c r="AV36" s="24"/>
-      <c r="AW36" s="15"/>
-      <c r="AX36" s="19"/>
-      <c r="AY36" s="15"/>
-      <c r="AZ36" s="15"/>
-      <c r="BA36" s="15"/>
-      <c r="BB36" s="15"/>
-      <c r="BC36" s="15"/>
-      <c r="BD36" s="15"/>
-      <c r="BE36" s="15"/>
-      <c r="BF36" s="15"/>
-      <c r="BG36" s="15"/>
-      <c r="BH36" s="15"/>
-      <c r="BI36" s="16"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="20"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
+      <c r="AG36" s="20"/>
+      <c r="AH36" s="20"/>
+      <c r="AI36" s="20"/>
+      <c r="AJ36" s="20"/>
+      <c r="AK36" s="20"/>
+      <c r="AL36" s="20"/>
+      <c r="AM36" s="20"/>
+      <c r="AN36" s="20"/>
+      <c r="AO36" s="20"/>
+      <c r="AP36" s="20"/>
+      <c r="AQ36" s="20"/>
+      <c r="AR36" s="20"/>
+      <c r="AS36" s="20"/>
+      <c r="AT36" s="20"/>
+      <c r="AU36" s="20"/>
+      <c r="AV36" s="20"/>
+      <c r="AW36" s="20"/>
+      <c r="AX36" s="20"/>
+      <c r="AY36" s="20"/>
+      <c r="AZ36" s="20"/>
+      <c r="BA36" s="20"/>
+      <c r="BB36" s="20"/>
+      <c r="BC36" s="20"/>
+      <c r="BD36" s="20"/>
+      <c r="BE36" s="20"/>
+      <c r="BF36" s="20"/>
+      <c r="BG36" s="20"/>
+      <c r="BH36" s="20"/>
+      <c r="BI36" s="20"/>
       <c r="BJ36" s="1"/>
       <c r="BK36" s="1"/>
       <c r="BL36" s="1"/>
@@ -12300,266 +12318,6 @@
       <c r="IV36" s="1"/>
       <c r="IW36" s="1"/>
       <c r="IX36" s="1"/>
-    </row>
-    <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="20"/>
-      <c r="AD37" s="20"/>
-      <c r="AE37" s="20"/>
-      <c r="AF37" s="20"/>
-      <c r="AG37" s="20"/>
-      <c r="AH37" s="20"/>
-      <c r="AI37" s="20"/>
-      <c r="AJ37" s="20"/>
-      <c r="AK37" s="20"/>
-      <c r="AL37" s="20"/>
-      <c r="AM37" s="20"/>
-      <c r="AN37" s="20"/>
-      <c r="AO37" s="20"/>
-      <c r="AP37" s="20"/>
-      <c r="AQ37" s="20"/>
-      <c r="AR37" s="20"/>
-      <c r="AS37" s="20"/>
-      <c r="AT37" s="20"/>
-      <c r="AU37" s="20"/>
-      <c r="AV37" s="20"/>
-      <c r="AW37" s="20"/>
-      <c r="AX37" s="20"/>
-      <c r="AY37" s="20"/>
-      <c r="AZ37" s="20"/>
-      <c r="BA37" s="20"/>
-      <c r="BB37" s="20"/>
-      <c r="BC37" s="20"/>
-      <c r="BD37" s="20"/>
-      <c r="BE37" s="20"/>
-      <c r="BF37" s="20"/>
-      <c r="BG37" s="20"/>
-      <c r="BH37" s="20"/>
-      <c r="BI37" s="20"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="1"/>
-      <c r="BM37" s="1"/>
-      <c r="BN37" s="1"/>
-      <c r="BO37" s="1"/>
-      <c r="BP37" s="1"/>
-      <c r="BQ37" s="1"/>
-      <c r="BR37" s="1"/>
-      <c r="BS37" s="1"/>
-      <c r="BT37" s="1"/>
-      <c r="BU37" s="1"/>
-      <c r="BV37" s="1"/>
-      <c r="BW37" s="1"/>
-      <c r="BX37" s="1"/>
-      <c r="BY37" s="1"/>
-      <c r="BZ37" s="1"/>
-      <c r="CA37" s="1"/>
-      <c r="CB37" s="1"/>
-      <c r="CC37" s="1"/>
-      <c r="CD37" s="1"/>
-      <c r="CE37" s="1"/>
-      <c r="CF37" s="1"/>
-      <c r="CG37" s="1"/>
-      <c r="CH37" s="1"/>
-      <c r="CI37" s="1"/>
-      <c r="CJ37" s="1"/>
-      <c r="CK37" s="1"/>
-      <c r="CL37" s="1"/>
-      <c r="CM37" s="1"/>
-      <c r="CN37" s="1"/>
-      <c r="CO37" s="1"/>
-      <c r="CP37" s="1"/>
-      <c r="CQ37" s="1"/>
-      <c r="CR37" s="1"/>
-      <c r="CS37" s="1"/>
-      <c r="CT37" s="1"/>
-      <c r="CU37" s="1"/>
-      <c r="CV37" s="1"/>
-      <c r="CW37" s="1"/>
-      <c r="CX37" s="1"/>
-      <c r="CY37" s="1"/>
-      <c r="CZ37" s="1"/>
-      <c r="DA37" s="1"/>
-      <c r="DB37" s="1"/>
-      <c r="DC37" s="1"/>
-      <c r="DD37" s="1"/>
-      <c r="DE37" s="1"/>
-      <c r="DF37" s="1"/>
-      <c r="DG37" s="1"/>
-      <c r="DH37" s="1"/>
-      <c r="DI37" s="1"/>
-      <c r="DJ37" s="1"/>
-      <c r="DK37" s="1"/>
-      <c r="DL37" s="1"/>
-      <c r="DM37" s="1"/>
-      <c r="DN37" s="1"/>
-      <c r="DO37" s="1"/>
-      <c r="DP37" s="1"/>
-      <c r="DQ37" s="1"/>
-      <c r="DR37" s="1"/>
-      <c r="DS37" s="1"/>
-      <c r="DT37" s="1"/>
-      <c r="DU37" s="1"/>
-      <c r="DV37" s="1"/>
-      <c r="DW37" s="1"/>
-      <c r="DX37" s="1"/>
-      <c r="DY37" s="1"/>
-      <c r="DZ37" s="1"/>
-      <c r="EA37" s="1"/>
-      <c r="EB37" s="1"/>
-      <c r="EC37" s="1"/>
-      <c r="ED37" s="1"/>
-      <c r="EE37" s="1"/>
-      <c r="EF37" s="1"/>
-      <c r="EG37" s="1"/>
-      <c r="EH37" s="1"/>
-      <c r="EI37" s="1"/>
-      <c r="EJ37" s="1"/>
-      <c r="EK37" s="1"/>
-      <c r="EL37" s="1"/>
-      <c r="EM37" s="1"/>
-      <c r="EN37" s="1"/>
-      <c r="EO37" s="1"/>
-      <c r="EP37" s="1"/>
-      <c r="EQ37" s="1"/>
-      <c r="ER37" s="1"/>
-      <c r="ES37" s="1"/>
-      <c r="ET37" s="1"/>
-      <c r="EU37" s="1"/>
-      <c r="EV37" s="1"/>
-      <c r="EW37" s="1"/>
-      <c r="EX37" s="1"/>
-      <c r="EY37" s="1"/>
-      <c r="EZ37" s="1"/>
-      <c r="FA37" s="1"/>
-      <c r="FB37" s="1"/>
-      <c r="FC37" s="1"/>
-      <c r="FD37" s="1"/>
-      <c r="FE37" s="1"/>
-      <c r="FF37" s="1"/>
-      <c r="FG37" s="1"/>
-      <c r="FH37" s="1"/>
-      <c r="FI37" s="1"/>
-      <c r="FJ37" s="1"/>
-      <c r="FK37" s="1"/>
-      <c r="FL37" s="1"/>
-      <c r="FM37" s="1"/>
-      <c r="FN37" s="1"/>
-      <c r="FO37" s="1"/>
-      <c r="FP37" s="1"/>
-      <c r="FQ37" s="1"/>
-      <c r="FR37" s="1"/>
-      <c r="FS37" s="1"/>
-      <c r="FT37" s="1"/>
-      <c r="FU37" s="1"/>
-      <c r="FV37" s="1"/>
-      <c r="FW37" s="1"/>
-      <c r="FX37" s="1"/>
-      <c r="FY37" s="1"/>
-      <c r="FZ37" s="1"/>
-      <c r="GA37" s="1"/>
-      <c r="GB37" s="1"/>
-      <c r="GC37" s="1"/>
-      <c r="GD37" s="1"/>
-      <c r="GE37" s="1"/>
-      <c r="GF37" s="1"/>
-      <c r="GG37" s="1"/>
-      <c r="GH37" s="1"/>
-      <c r="GI37" s="1"/>
-      <c r="GJ37" s="1"/>
-      <c r="GK37" s="1"/>
-      <c r="GL37" s="1"/>
-      <c r="GM37" s="1"/>
-      <c r="GN37" s="1"/>
-      <c r="GO37" s="1"/>
-      <c r="GP37" s="1"/>
-      <c r="GQ37" s="1"/>
-      <c r="GR37" s="1"/>
-      <c r="GS37" s="1"/>
-      <c r="GT37" s="1"/>
-      <c r="GU37" s="1"/>
-      <c r="GV37" s="1"/>
-      <c r="GW37" s="1"/>
-      <c r="GX37" s="1"/>
-      <c r="GY37" s="1"/>
-      <c r="GZ37" s="1"/>
-      <c r="HA37" s="1"/>
-      <c r="HB37" s="1"/>
-      <c r="HC37" s="1"/>
-      <c r="HD37" s="1"/>
-      <c r="HE37" s="1"/>
-      <c r="HF37" s="1"/>
-      <c r="HG37" s="1"/>
-      <c r="HH37" s="1"/>
-      <c r="HI37" s="1"/>
-      <c r="HJ37" s="1"/>
-      <c r="HK37" s="1"/>
-      <c r="HL37" s="1"/>
-      <c r="HM37" s="1"/>
-      <c r="HN37" s="1"/>
-      <c r="HO37" s="1"/>
-      <c r="HP37" s="1"/>
-      <c r="HQ37" s="1"/>
-      <c r="HR37" s="1"/>
-      <c r="HS37" s="1"/>
-      <c r="HT37" s="1"/>
-      <c r="HU37" s="1"/>
-      <c r="HV37" s="1"/>
-      <c r="HW37" s="1"/>
-      <c r="HX37" s="1"/>
-      <c r="HY37" s="1"/>
-      <c r="HZ37" s="1"/>
-      <c r="IA37" s="1"/>
-      <c r="IB37" s="1"/>
-      <c r="IC37" s="1"/>
-      <c r="ID37" s="1"/>
-      <c r="IE37" s="1"/>
-      <c r="IF37" s="1"/>
-      <c r="IG37" s="1"/>
-      <c r="IH37" s="1"/>
-      <c r="II37" s="1"/>
-      <c r="IJ37" s="1"/>
-      <c r="IK37" s="1"/>
-      <c r="IL37" s="1"/>
-      <c r="IM37" s="1"/>
-      <c r="IN37" s="1"/>
-      <c r="IO37" s="1"/>
-      <c r="IP37" s="1"/>
-      <c r="IQ37" s="1"/>
-      <c r="IR37" s="1"/>
-      <c r="IS37" s="1"/>
-      <c r="IT37" s="1"/>
-      <c r="IU37" s="1"/>
-      <c r="IV37" s="1"/>
-      <c r="IW37" s="1"/>
-      <c r="IX37" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="61">

--- a/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Servlet/MainServlet_クラス仕様書.xlsx
+++ b/020-内部_プログラミング設計/022-クラス仕様書/商品検索機能/Servlet/MainServlet_クラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D145E875-C52E-4286-AA15-683A13EA296E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7E1113-0A6A-4F49-9C0A-21A5DC8D800C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -240,10 +240,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>1.1　requestとresoponseの文字コードをUTF-8に指定</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>ログイン情報</t>
     <rPh sb="4" eb="6">
       <t>ジョウホウ</t>
@@ -259,13 +255,6 @@
   </si>
   <si>
     <t>変数</t>
-  </si>
-  <si>
-    <t>・リクエスト情報 response</t>
-    <rPh sb="6" eb="8">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>・レスポンス情報 response</t>
@@ -491,6 +480,17 @@
     <rPh sb="42" eb="43">
       <t>ダ</t>
     </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>・リクエスト情報 request</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1.1　requestとresponseの文字コードをUTF-8に指定</t>
     <phoneticPr fontId="7"/>
   </si>
 </sst>
@@ -1038,38 +1038,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1092,16 +1098,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1469,71 +1469,71 @@
       <c r="J1" s="58"/>
       <c r="K1" s="58"/>
       <c r="L1" s="58"/>
-      <c r="M1" s="60" t="s">
+      <c r="M1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="59" t="s">
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="60" t="s">
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="59" t="s">
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="59"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="60" t="s">
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="59" t="s">
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54"/>
+      <c r="AT1" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="59"/>
-      <c r="AX1" s="59"/>
-      <c r="AY1" s="59"/>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="60" t="s">
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="57">
+      <c r="BB1" s="54"/>
+      <c r="BC1" s="54"/>
+      <c r="BD1" s="56">
         <v>45554</v>
       </c>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
+      <c r="BE1" s="56"/>
+      <c r="BF1" s="56"/>
+      <c r="BG1" s="56"/>
+      <c r="BH1" s="56"/>
+      <c r="BI1" s="56"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1745,66 +1745,66 @@
       <c r="J2" s="58"/>
       <c r="K2" s="58"/>
       <c r="L2" s="58"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="60" t="s">
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="59" t="str">
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55" t="str">
         <f>クラス仕様!G5</f>
         <v>MainServlet</v>
       </c>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="60" t="s">
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="60" t="s">
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="57"/>
-      <c r="BI2" s="57"/>
+      <c r="BB2" s="54"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="56"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="56"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -2004,1114 +2004,1148 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="55" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="55"/>
-      <c r="AJ4" s="55"/>
-      <c r="AK4" s="55"/>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="55"/>
-      <c r="AN4" s="55"/>
-      <c r="AO4" s="55"/>
-      <c r="AP4" s="55"/>
-      <c r="AQ4" s="55"/>
-      <c r="AR4" s="55"/>
-      <c r="AS4" s="55"/>
-      <c r="AT4" s="55"/>
-      <c r="AU4" s="55"/>
-      <c r="AV4" s="55"/>
-      <c r="AW4" s="55"/>
-      <c r="AX4" s="55"/>
-      <c r="AY4" s="55"/>
-      <c r="AZ4" s="55"/>
-      <c r="BA4" s="55"/>
-      <c r="BB4" s="55"/>
-      <c r="BC4" s="55"/>
-      <c r="BD4" s="55"/>
-      <c r="BE4" s="55"/>
-      <c r="BF4" s="55"/>
-      <c r="BG4" s="55"/>
-      <c r="BH4" s="55"/>
-      <c r="BI4" s="55"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="61"/>
+      <c r="Z4" s="61"/>
+      <c r="AA4" s="61"/>
+      <c r="AB4" s="61"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61"/>
+      <c r="AM4" s="61"/>
+      <c r="AN4" s="61"/>
+      <c r="AO4" s="61"/>
+      <c r="AP4" s="61"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="61"/>
+      <c r="AT4" s="61"/>
+      <c r="AU4" s="61"/>
+      <c r="AV4" s="61"/>
+      <c r="AW4" s="61"/>
+      <c r="AX4" s="61"/>
+      <c r="AY4" s="61"/>
+      <c r="AZ4" s="61"/>
+      <c r="BA4" s="61"/>
+      <c r="BB4" s="61"/>
+      <c r="BC4" s="61"/>
+      <c r="BD4" s="61"/>
+      <c r="BE4" s="61"/>
+      <c r="BF4" s="61"/>
+      <c r="BG4" s="61"/>
+      <c r="BH4" s="61"/>
+      <c r="BI4" s="61"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="55"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="55"/>
-      <c r="AH5" s="55"/>
-      <c r="AI5" s="55"/>
-      <c r="AJ5" s="55"/>
-      <c r="AK5" s="55"/>
-      <c r="AL5" s="55"/>
-      <c r="AM5" s="55"/>
-      <c r="AN5" s="55"/>
-      <c r="AO5" s="55"/>
-      <c r="AP5" s="55"/>
-      <c r="AQ5" s="55"/>
-      <c r="AR5" s="55"/>
-      <c r="AS5" s="55"/>
-      <c r="AT5" s="55"/>
-      <c r="AU5" s="55"/>
-      <c r="AV5" s="55"/>
-      <c r="AW5" s="55"/>
-      <c r="AX5" s="55"/>
-      <c r="AY5" s="55"/>
-      <c r="AZ5" s="55"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="55"/>
-      <c r="BC5" s="55"/>
-      <c r="BD5" s="55"/>
-      <c r="BE5" s="55"/>
-      <c r="BF5" s="55"/>
-      <c r="BG5" s="55"/>
-      <c r="BH5" s="55"/>
-      <c r="BI5" s="55"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="61"/>
+      <c r="AB5" s="61"/>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="61"/>
+      <c r="AS5" s="61"/>
+      <c r="AT5" s="61"/>
+      <c r="AU5" s="61"/>
+      <c r="AV5" s="61"/>
+      <c r="AW5" s="61"/>
+      <c r="AX5" s="61"/>
+      <c r="AY5" s="61"/>
+      <c r="AZ5" s="61"/>
+      <c r="BA5" s="61"/>
+      <c r="BB5" s="61"/>
+      <c r="BC5" s="61"/>
+      <c r="BD5" s="61"/>
+      <c r="BE5" s="61"/>
+      <c r="BF5" s="61"/>
+      <c r="BG5" s="61"/>
+      <c r="BH5" s="61"/>
+      <c r="BI5" s="61"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="55" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-      <c r="Z6" s="55"/>
-      <c r="AA6" s="55"/>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="55"/>
-      <c r="AD6" s="56" t="s">
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="61"/>
+      <c r="Z6" s="61"/>
+      <c r="AA6" s="61"/>
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="61"/>
+      <c r="AD6" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="AE6" s="56"/>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="56"/>
-      <c r="AH6" s="56"/>
-      <c r="AI6" s="56"/>
-      <c r="AJ6" s="55" t="s">
+      <c r="AE6" s="60"/>
+      <c r="AF6" s="60"/>
+      <c r="AG6" s="60"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AJ6" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="AK6" s="55"/>
-      <c r="AL6" s="55"/>
-      <c r="AM6" s="55"/>
-      <c r="AN6" s="55"/>
-      <c r="AO6" s="55"/>
-      <c r="AP6" s="55"/>
-      <c r="AQ6" s="55"/>
-      <c r="AR6" s="55"/>
-      <c r="AS6" s="55"/>
-      <c r="AT6" s="55"/>
-      <c r="AU6" s="55"/>
-      <c r="AV6" s="55"/>
-      <c r="AW6" s="55"/>
-      <c r="AX6" s="55"/>
-      <c r="AY6" s="55"/>
-      <c r="AZ6" s="55"/>
-      <c r="BA6" s="55"/>
-      <c r="BB6" s="55"/>
-      <c r="BC6" s="55"/>
-      <c r="BD6" s="55"/>
-      <c r="BE6" s="55"/>
-      <c r="BF6" s="55"/>
-      <c r="BG6" s="55"/>
-      <c r="BH6" s="55"/>
-      <c r="BI6" s="55"/>
+      <c r="AK6" s="61"/>
+      <c r="AL6" s="61"/>
+      <c r="AM6" s="61"/>
+      <c r="AN6" s="61"/>
+      <c r="AO6" s="61"/>
+      <c r="AP6" s="61"/>
+      <c r="AQ6" s="61"/>
+      <c r="AR6" s="61"/>
+      <c r="AS6" s="61"/>
+      <c r="AT6" s="61"/>
+      <c r="AU6" s="61"/>
+      <c r="AV6" s="61"/>
+      <c r="AW6" s="61"/>
+      <c r="AX6" s="61"/>
+      <c r="AY6" s="61"/>
+      <c r="AZ6" s="61"/>
+      <c r="BA6" s="61"/>
+      <c r="BB6" s="61"/>
+      <c r="BC6" s="61"/>
+      <c r="BD6" s="61"/>
+      <c r="BE6" s="61"/>
+      <c r="BF6" s="61"/>
+      <c r="BG6" s="61"/>
+      <c r="BH6" s="61"/>
+      <c r="BI6" s="61"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56" t="s">
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="60"/>
+      <c r="O8" s="60"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56" t="s">
+      <c r="V8" s="60"/>
+      <c r="W8" s="60"/>
+      <c r="X8" s="60"/>
+      <c r="Y8" s="60"/>
+      <c r="Z8" s="60"/>
+      <c r="AA8" s="60"/>
+      <c r="AB8" s="60"/>
+      <c r="AC8" s="60"/>
+      <c r="AD8" s="60"/>
+      <c r="AE8" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="56"/>
-      <c r="AL8" s="56"/>
-      <c r="AM8" s="56"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="56" t="s">
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="AP8" s="56"/>
-      <c r="AQ8" s="56"/>
-      <c r="AR8" s="56"/>
-      <c r="AS8" s="56"/>
-      <c r="AT8" s="56"/>
-      <c r="AU8" s="56"/>
-      <c r="AV8" s="56"/>
-      <c r="AW8" s="56"/>
-      <c r="AX8" s="56"/>
-      <c r="AY8" s="56"/>
-      <c r="AZ8" s="56"/>
-      <c r="BA8" s="56"/>
-      <c r="BB8" s="56"/>
-      <c r="BC8" s="56"/>
-      <c r="BD8" s="56"/>
-      <c r="BE8" s="56"/>
-      <c r="BF8" s="56"/>
-      <c r="BG8" s="56"/>
-      <c r="BH8" s="56"/>
-      <c r="BI8" s="56"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+      <c r="BC8" s="60"/>
+      <c r="BD8" s="60"/>
+      <c r="BE8" s="60"/>
+      <c r="BF8" s="60"/>
+      <c r="BG8" s="60"/>
+      <c r="BH8" s="60"/>
+      <c r="BI8" s="60"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="54"/>
-      <c r="AB9" s="54"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="54"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="54"/>
-      <c r="AH9" s="54"/>
-      <c r="AI9" s="54"/>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="54"/>
-      <c r="AL9" s="54"/>
-      <c r="AM9" s="54"/>
-      <c r="AN9" s="54"/>
-      <c r="AO9" s="54"/>
-      <c r="AP9" s="54"/>
-      <c r="AQ9" s="54"/>
-      <c r="AR9" s="54"/>
-      <c r="AS9" s="54"/>
-      <c r="AT9" s="54"/>
-      <c r="AU9" s="54"/>
-      <c r="AV9" s="54"/>
-      <c r="AW9" s="54"/>
-      <c r="AX9" s="54"/>
-      <c r="AY9" s="54"/>
-      <c r="AZ9" s="54"/>
-      <c r="BA9" s="54"/>
-      <c r="BB9" s="54"/>
-      <c r="BC9" s="54"/>
-      <c r="BD9" s="54"/>
-      <c r="BE9" s="54"/>
-      <c r="BF9" s="54"/>
-      <c r="BG9" s="54"/>
-      <c r="BH9" s="54"/>
-      <c r="BI9" s="54"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="57"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
+      <c r="AA9" s="57"/>
+      <c r="AB9" s="57"/>
+      <c r="AC9" s="57"/>
+      <c r="AD9" s="57"/>
+      <c r="AE9" s="57"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="57"/>
+      <c r="AH9" s="57"/>
+      <c r="AI9" s="57"/>
+      <c r="AJ9" s="57"/>
+      <c r="AK9" s="57"/>
+      <c r="AL9" s="57"/>
+      <c r="AM9" s="57"/>
+      <c r="AN9" s="57"/>
+      <c r="AO9" s="57"/>
+      <c r="AP9" s="57"/>
+      <c r="AQ9" s="57"/>
+      <c r="AR9" s="57"/>
+      <c r="AS9" s="57"/>
+      <c r="AT9" s="57"/>
+      <c r="AU9" s="57"/>
+      <c r="AV9" s="57"/>
+      <c r="AW9" s="57"/>
+      <c r="AX9" s="57"/>
+      <c r="AY9" s="57"/>
+      <c r="AZ9" s="57"/>
+      <c r="BA9" s="57"/>
+      <c r="BB9" s="57"/>
+      <c r="BC9" s="57"/>
+      <c r="BD9" s="57"/>
+      <c r="BE9" s="57"/>
+      <c r="BF9" s="57"/>
+      <c r="BG9" s="57"/>
+      <c r="BH9" s="57"/>
+      <c r="BI9" s="57"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="54"/>
-      <c r="Z10" s="54"/>
-      <c r="AA10" s="54"/>
-      <c r="AB10" s="54"/>
-      <c r="AC10" s="54"/>
-      <c r="AD10" s="54"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="54"/>
-      <c r="AG10" s="54"/>
-      <c r="AH10" s="54"/>
-      <c r="AI10" s="54"/>
-      <c r="AJ10" s="54"/>
-      <c r="AK10" s="54"/>
-      <c r="AL10" s="54"/>
-      <c r="AM10" s="54"/>
-      <c r="AN10" s="54"/>
-      <c r="AO10" s="54"/>
-      <c r="AP10" s="54"/>
-      <c r="AQ10" s="54"/>
-      <c r="AR10" s="54"/>
-      <c r="AS10" s="54"/>
-      <c r="AT10" s="54"/>
-      <c r="AU10" s="54"/>
-      <c r="AV10" s="54"/>
-      <c r="AW10" s="54"/>
-      <c r="AX10" s="54"/>
-      <c r="AY10" s="54"/>
-      <c r="AZ10" s="54"/>
-      <c r="BA10" s="54"/>
-      <c r="BB10" s="54"/>
-      <c r="BC10" s="54"/>
-      <c r="BD10" s="54"/>
-      <c r="BE10" s="54"/>
-      <c r="BF10" s="54"/>
-      <c r="BG10" s="54"/>
-      <c r="BH10" s="54"/>
-      <c r="BI10" s="54"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="57"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="57"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+      <c r="AA10" s="57"/>
+      <c r="AB10" s="57"/>
+      <c r="AC10" s="57"/>
+      <c r="AD10" s="57"/>
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="57"/>
+      <c r="AG10" s="57"/>
+      <c r="AH10" s="57"/>
+      <c r="AI10" s="57"/>
+      <c r="AJ10" s="57"/>
+      <c r="AK10" s="57"/>
+      <c r="AL10" s="57"/>
+      <c r="AM10" s="57"/>
+      <c r="AN10" s="57"/>
+      <c r="AO10" s="57"/>
+      <c r="AP10" s="57"/>
+      <c r="AQ10" s="57"/>
+      <c r="AR10" s="57"/>
+      <c r="AS10" s="57"/>
+      <c r="AT10" s="57"/>
+      <c r="AU10" s="57"/>
+      <c r="AV10" s="57"/>
+      <c r="AW10" s="57"/>
+      <c r="AX10" s="57"/>
+      <c r="AY10" s="57"/>
+      <c r="AZ10" s="57"/>
+      <c r="BA10" s="57"/>
+      <c r="BB10" s="57"/>
+      <c r="BC10" s="57"/>
+      <c r="BD10" s="57"/>
+      <c r="BE10" s="57"/>
+      <c r="BF10" s="57"/>
+      <c r="BG10" s="57"/>
+      <c r="BH10" s="57"/>
+      <c r="BI10" s="57"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="54"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="54"/>
-      <c r="AH11" s="54"/>
-      <c r="AI11" s="54"/>
-      <c r="AJ11" s="54"/>
-      <c r="AK11" s="54"/>
-      <c r="AL11" s="54"/>
-      <c r="AM11" s="54"/>
-      <c r="AN11" s="54"/>
-      <c r="AO11" s="54"/>
-      <c r="AP11" s="54"/>
-      <c r="AQ11" s="54"/>
-      <c r="AR11" s="54"/>
-      <c r="AS11" s="54"/>
-      <c r="AT11" s="54"/>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="54"/>
-      <c r="AW11" s="54"/>
-      <c r="AX11" s="54"/>
-      <c r="AY11" s="54"/>
-      <c r="AZ11" s="54"/>
-      <c r="BA11" s="54"/>
-      <c r="BB11" s="54"/>
-      <c r="BC11" s="54"/>
-      <c r="BD11" s="54"/>
-      <c r="BE11" s="54"/>
-      <c r="BF11" s="54"/>
-      <c r="BG11" s="54"/>
-      <c r="BH11" s="54"/>
-      <c r="BI11" s="54"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="57"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="57"/>
+      <c r="AC11" s="57"/>
+      <c r="AD11" s="57"/>
+      <c r="AE11" s="57"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="57"/>
+      <c r="AI11" s="57"/>
+      <c r="AJ11" s="57"/>
+      <c r="AK11" s="57"/>
+      <c r="AL11" s="57"/>
+      <c r="AM11" s="57"/>
+      <c r="AN11" s="57"/>
+      <c r="AO11" s="57"/>
+      <c r="AP11" s="57"/>
+      <c r="AQ11" s="57"/>
+      <c r="AR11" s="57"/>
+      <c r="AS11" s="57"/>
+      <c r="AT11" s="57"/>
+      <c r="AU11" s="57"/>
+      <c r="AV11" s="57"/>
+      <c r="AW11" s="57"/>
+      <c r="AX11" s="57"/>
+      <c r="AY11" s="57"/>
+      <c r="AZ11" s="57"/>
+      <c r="BA11" s="57"/>
+      <c r="BB11" s="57"/>
+      <c r="BC11" s="57"/>
+      <c r="BD11" s="57"/>
+      <c r="BE11" s="57"/>
+      <c r="BF11" s="57"/>
+      <c r="BG11" s="57"/>
+      <c r="BH11" s="57"/>
+      <c r="BI11" s="57"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="54"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="54"/>
-      <c r="AC12" s="54"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="54"/>
-      <c r="AO12" s="54"/>
-      <c r="AP12" s="54"/>
-      <c r="AQ12" s="54"/>
-      <c r="AR12" s="54"/>
-      <c r="AS12" s="54"/>
-      <c r="AT12" s="54"/>
-      <c r="AU12" s="54"/>
-      <c r="AV12" s="54"/>
-      <c r="AW12" s="54"/>
-      <c r="AX12" s="54"/>
-      <c r="AY12" s="54"/>
-      <c r="AZ12" s="54"/>
-      <c r="BA12" s="54"/>
-      <c r="BB12" s="54"/>
-      <c r="BC12" s="54"/>
-      <c r="BD12" s="54"/>
-      <c r="BE12" s="54"/>
-      <c r="BF12" s="54"/>
-      <c r="BG12" s="54"/>
-      <c r="BH12" s="54"/>
-      <c r="BI12" s="54"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="57"/>
+      <c r="AG12" s="57"/>
+      <c r="AH12" s="57"/>
+      <c r="AI12" s="57"/>
+      <c r="AJ12" s="57"/>
+      <c r="AK12" s="57"/>
+      <c r="AL12" s="57"/>
+      <c r="AM12" s="57"/>
+      <c r="AN12" s="57"/>
+      <c r="AO12" s="57"/>
+      <c r="AP12" s="57"/>
+      <c r="AQ12" s="57"/>
+      <c r="AR12" s="57"/>
+      <c r="AS12" s="57"/>
+      <c r="AT12" s="57"/>
+      <c r="AU12" s="57"/>
+      <c r="AV12" s="57"/>
+      <c r="AW12" s="57"/>
+      <c r="AX12" s="57"/>
+      <c r="AY12" s="57"/>
+      <c r="AZ12" s="57"/>
+      <c r="BA12" s="57"/>
+      <c r="BB12" s="57"/>
+      <c r="BC12" s="57"/>
+      <c r="BD12" s="57"/>
+      <c r="BE12" s="57"/>
+      <c r="BF12" s="57"/>
+      <c r="BG12" s="57"/>
+      <c r="BH12" s="57"/>
+      <c r="BI12" s="57"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="54"/>
-      <c r="X13" s="54"/>
-      <c r="Y13" s="54"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="54"/>
-      <c r="AC13" s="54"/>
-      <c r="AD13" s="54"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="54"/>
-      <c r="AH13" s="54"/>
-      <c r="AI13" s="54"/>
-      <c r="AJ13" s="54"/>
-      <c r="AK13" s="54"/>
-      <c r="AL13" s="54"/>
-      <c r="AM13" s="54"/>
-      <c r="AN13" s="54"/>
-      <c r="AO13" s="54"/>
-      <c r="AP13" s="54"/>
-      <c r="AQ13" s="54"/>
-      <c r="AR13" s="54"/>
-      <c r="AS13" s="54"/>
-      <c r="AT13" s="54"/>
-      <c r="AU13" s="54"/>
-      <c r="AV13" s="54"/>
-      <c r="AW13" s="54"/>
-      <c r="AX13" s="54"/>
-      <c r="AY13" s="54"/>
-      <c r="AZ13" s="54"/>
-      <c r="BA13" s="54"/>
-      <c r="BB13" s="54"/>
-      <c r="BC13" s="54"/>
-      <c r="BD13" s="54"/>
-      <c r="BE13" s="54"/>
-      <c r="BF13" s="54"/>
-      <c r="BG13" s="54"/>
-      <c r="BH13" s="54"/>
-      <c r="BI13" s="54"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="57"/>
+      <c r="Y13" s="57"/>
+      <c r="Z13" s="57"/>
+      <c r="AA13" s="57"/>
+      <c r="AB13" s="57"/>
+      <c r="AC13" s="57"/>
+      <c r="AD13" s="57"/>
+      <c r="AE13" s="57"/>
+      <c r="AF13" s="57"/>
+      <c r="AG13" s="57"/>
+      <c r="AH13" s="57"/>
+      <c r="AI13" s="57"/>
+      <c r="AJ13" s="57"/>
+      <c r="AK13" s="57"/>
+      <c r="AL13" s="57"/>
+      <c r="AM13" s="57"/>
+      <c r="AN13" s="57"/>
+      <c r="AO13" s="57"/>
+      <c r="AP13" s="57"/>
+      <c r="AQ13" s="57"/>
+      <c r="AR13" s="57"/>
+      <c r="AS13" s="57"/>
+      <c r="AT13" s="57"/>
+      <c r="AU13" s="57"/>
+      <c r="AV13" s="57"/>
+      <c r="AW13" s="57"/>
+      <c r="AX13" s="57"/>
+      <c r="AY13" s="57"/>
+      <c r="AZ13" s="57"/>
+      <c r="BA13" s="57"/>
+      <c r="BB13" s="57"/>
+      <c r="BC13" s="57"/>
+      <c r="BD13" s="57"/>
+      <c r="BE13" s="57"/>
+      <c r="BF13" s="57"/>
+      <c r="BG13" s="57"/>
+      <c r="BH13" s="57"/>
+      <c r="BI13" s="57"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="54"/>
-      <c r="W14" s="54"/>
-      <c r="X14" s="54"/>
-      <c r="Y14" s="54"/>
-      <c r="Z14" s="54"/>
-      <c r="AA14" s="54"/>
-      <c r="AB14" s="54"/>
-      <c r="AC14" s="54"/>
-      <c r="AD14" s="54"/>
-      <c r="AE14" s="54"/>
-      <c r="AF14" s="54"/>
-      <c r="AG14" s="54"/>
-      <c r="AH14" s="54"/>
-      <c r="AI14" s="54"/>
-      <c r="AJ14" s="54"/>
-      <c r="AK14" s="54"/>
-      <c r="AL14" s="54"/>
-      <c r="AM14" s="54"/>
-      <c r="AN14" s="54"/>
-      <c r="AO14" s="54"/>
-      <c r="AP14" s="54"/>
-      <c r="AQ14" s="54"/>
-      <c r="AR14" s="54"/>
-      <c r="AS14" s="54"/>
-      <c r="AT14" s="54"/>
-      <c r="AU14" s="54"/>
-      <c r="AV14" s="54"/>
-      <c r="AW14" s="54"/>
-      <c r="AX14" s="54"/>
-      <c r="AY14" s="54"/>
-      <c r="AZ14" s="54"/>
-      <c r="BA14" s="54"/>
-      <c r="BB14" s="54"/>
-      <c r="BC14" s="54"/>
-      <c r="BD14" s="54"/>
-      <c r="BE14" s="54"/>
-      <c r="BF14" s="54"/>
-      <c r="BG14" s="54"/>
-      <c r="BH14" s="54"/>
-      <c r="BI14" s="54"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+      <c r="AA14" s="57"/>
+      <c r="AB14" s="57"/>
+      <c r="AC14" s="57"/>
+      <c r="AD14" s="57"/>
+      <c r="AE14" s="57"/>
+      <c r="AF14" s="57"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="57"/>
+      <c r="AI14" s="57"/>
+      <c r="AJ14" s="57"/>
+      <c r="AK14" s="57"/>
+      <c r="AL14" s="57"/>
+      <c r="AM14" s="57"/>
+      <c r="AN14" s="57"/>
+      <c r="AO14" s="57"/>
+      <c r="AP14" s="57"/>
+      <c r="AQ14" s="57"/>
+      <c r="AR14" s="57"/>
+      <c r="AS14" s="57"/>
+      <c r="AT14" s="57"/>
+      <c r="AU14" s="57"/>
+      <c r="AV14" s="57"/>
+      <c r="AW14" s="57"/>
+      <c r="AX14" s="57"/>
+      <c r="AY14" s="57"/>
+      <c r="AZ14" s="57"/>
+      <c r="BA14" s="57"/>
+      <c r="BB14" s="57"/>
+      <c r="BC14" s="57"/>
+      <c r="BD14" s="57"/>
+      <c r="BE14" s="57"/>
+      <c r="BF14" s="57"/>
+      <c r="BG14" s="57"/>
+      <c r="BH14" s="57"/>
+      <c r="BI14" s="57"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="56"/>
-      <c r="Y16" s="56"/>
-      <c r="Z16" s="56"/>
-      <c r="AA16" s="56"/>
-      <c r="AB16" s="56"/>
-      <c r="AC16" s="56"/>
-      <c r="AD16" s="56"/>
-      <c r="AE16" s="56"/>
-      <c r="AF16" s="56"/>
-      <c r="AG16" s="56"/>
-      <c r="AH16" s="56"/>
-      <c r="AI16" s="56"/>
-      <c r="AJ16" s="56"/>
-      <c r="AK16" s="56"/>
-      <c r="AL16" s="56"/>
-      <c r="AM16" s="56"/>
-      <c r="AN16" s="56"/>
-      <c r="AO16" s="56"/>
-      <c r="AP16" s="56"/>
-      <c r="AQ16" s="56"/>
-      <c r="AR16" s="56"/>
-      <c r="AS16" s="56"/>
-      <c r="AT16" s="56"/>
-      <c r="AU16" s="56"/>
-      <c r="AV16" s="56"/>
-      <c r="AW16" s="56"/>
-      <c r="AX16" s="56"/>
-      <c r="AY16" s="56"/>
-      <c r="AZ16" s="56"/>
-      <c r="BA16" s="56"/>
-      <c r="BB16" s="56"/>
-      <c r="BC16" s="56"/>
-      <c r="BD16" s="56"/>
-      <c r="BE16" s="56"/>
-      <c r="BF16" s="56"/>
-      <c r="BG16" s="56"/>
-      <c r="BH16" s="56"/>
-      <c r="BI16" s="56"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="60"/>
+      <c r="Z16" s="60"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="60"/>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="60"/>
+      <c r="AE16" s="60"/>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+      <c r="BC16" s="60"/>
+      <c r="BD16" s="60"/>
+      <c r="BE16" s="60"/>
+      <c r="BF16" s="60"/>
+      <c r="BG16" s="60"/>
+      <c r="BH16" s="60"/>
+      <c r="BI16" s="60"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
-        <v>82</v>
+      <c r="A17" s="61" t="s">
+        <v>80</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-      <c r="X17" s="54"/>
-      <c r="Y17" s="54"/>
-      <c r="Z17" s="54"/>
-      <c r="AA17" s="54"/>
-      <c r="AB17" s="54"/>
-      <c r="AC17" s="54"/>
-      <c r="AD17" s="54"/>
-      <c r="AE17" s="54"/>
-      <c r="AF17" s="54"/>
-      <c r="AG17" s="54"/>
-      <c r="AH17" s="54"/>
-      <c r="AI17" s="54"/>
-      <c r="AJ17" s="54"/>
-      <c r="AK17" s="54"/>
-      <c r="AL17" s="54"/>
-      <c r="AM17" s="54"/>
-      <c r="AN17" s="54"/>
-      <c r="AO17" s="54"/>
-      <c r="AP17" s="54"/>
-      <c r="AQ17" s="54"/>
-      <c r="AR17" s="54"/>
-      <c r="AS17" s="54"/>
-      <c r="AT17" s="54"/>
-      <c r="AU17" s="54"/>
-      <c r="AV17" s="54"/>
-      <c r="AW17" s="54"/>
-      <c r="AX17" s="54"/>
-      <c r="AY17" s="54"/>
-      <c r="AZ17" s="54"/>
-      <c r="BA17" s="54"/>
-      <c r="BB17" s="54"/>
-      <c r="BC17" s="54"/>
-      <c r="BD17" s="54"/>
-      <c r="BE17" s="54"/>
-      <c r="BF17" s="54"/>
-      <c r="BG17" s="54"/>
-      <c r="BH17" s="54"/>
-      <c r="BI17" s="54"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="57"/>
+      <c r="Y17" s="57"/>
+      <c r="Z17" s="57"/>
+      <c r="AA17" s="57"/>
+      <c r="AB17" s="57"/>
+      <c r="AC17" s="57"/>
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="57"/>
+      <c r="AF17" s="57"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="57"/>
+      <c r="AI17" s="57"/>
+      <c r="AJ17" s="57"/>
+      <c r="AK17" s="57"/>
+      <c r="AL17" s="57"/>
+      <c r="AM17" s="57"/>
+      <c r="AN17" s="57"/>
+      <c r="AO17" s="57"/>
+      <c r="AP17" s="57"/>
+      <c r="AQ17" s="57"/>
+      <c r="AR17" s="57"/>
+      <c r="AS17" s="57"/>
+      <c r="AT17" s="57"/>
+      <c r="AU17" s="57"/>
+      <c r="AV17" s="57"/>
+      <c r="AW17" s="57"/>
+      <c r="AX17" s="57"/>
+      <c r="AY17" s="57"/>
+      <c r="AZ17" s="57"/>
+      <c r="BA17" s="57"/>
+      <c r="BB17" s="57"/>
+      <c r="BC17" s="57"/>
+      <c r="BD17" s="57"/>
+      <c r="BE17" s="57"/>
+      <c r="BF17" s="57"/>
+      <c r="BG17" s="57"/>
+      <c r="BH17" s="57"/>
+      <c r="BI17" s="57"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="54"/>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="54"/>
-      <c r="Z18" s="54"/>
-      <c r="AA18" s="54"/>
-      <c r="AB18" s="54"/>
-      <c r="AC18" s="54"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="54"/>
-      <c r="AF18" s="54"/>
-      <c r="AG18" s="54"/>
-      <c r="AH18" s="54"/>
-      <c r="AI18" s="54"/>
-      <c r="AJ18" s="54"/>
-      <c r="AK18" s="54"/>
-      <c r="AL18" s="54"/>
-      <c r="AM18" s="54"/>
-      <c r="AN18" s="54"/>
-      <c r="AO18" s="54"/>
-      <c r="AP18" s="54"/>
-      <c r="AQ18" s="54"/>
-      <c r="AR18" s="54"/>
-      <c r="AS18" s="54"/>
-      <c r="AT18" s="54"/>
-      <c r="AU18" s="54"/>
-      <c r="AV18" s="54"/>
-      <c r="AW18" s="54"/>
-      <c r="AX18" s="54"/>
-      <c r="AY18" s="54"/>
-      <c r="AZ18" s="54"/>
-      <c r="BA18" s="54"/>
-      <c r="BB18" s="54"/>
-      <c r="BC18" s="54"/>
-      <c r="BD18" s="54"/>
-      <c r="BE18" s="54"/>
-      <c r="BF18" s="54"/>
-      <c r="BG18" s="54"/>
-      <c r="BH18" s="54"/>
-      <c r="BI18" s="54"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="57"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="57"/>
+      <c r="Y18" s="57"/>
+      <c r="Z18" s="57"/>
+      <c r="AA18" s="57"/>
+      <c r="AB18" s="57"/>
+      <c r="AC18" s="57"/>
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="57"/>
+      <c r="AF18" s="57"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="57"/>
+      <c r="AI18" s="57"/>
+      <c r="AJ18" s="57"/>
+      <c r="AK18" s="57"/>
+      <c r="AL18" s="57"/>
+      <c r="AM18" s="57"/>
+      <c r="AN18" s="57"/>
+      <c r="AO18" s="57"/>
+      <c r="AP18" s="57"/>
+      <c r="AQ18" s="57"/>
+      <c r="AR18" s="57"/>
+      <c r="AS18" s="57"/>
+      <c r="AT18" s="57"/>
+      <c r="AU18" s="57"/>
+      <c r="AV18" s="57"/>
+      <c r="AW18" s="57"/>
+      <c r="AX18" s="57"/>
+      <c r="AY18" s="57"/>
+      <c r="AZ18" s="57"/>
+      <c r="BA18" s="57"/>
+      <c r="BB18" s="57"/>
+      <c r="BC18" s="57"/>
+      <c r="BD18" s="57"/>
+      <c r="BE18" s="57"/>
+      <c r="BF18" s="57"/>
+      <c r="BG18" s="57"/>
+      <c r="BH18" s="57"/>
+      <c r="BI18" s="57"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="54"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="54"/>
-      <c r="X19" s="54"/>
-      <c r="Y19" s="54"/>
-      <c r="Z19" s="54"/>
-      <c r="AA19" s="54"/>
-      <c r="AB19" s="54"/>
-      <c r="AC19" s="54"/>
-      <c r="AD19" s="54"/>
-      <c r="AE19" s="54"/>
-      <c r="AF19" s="54"/>
-      <c r="AG19" s="54"/>
-      <c r="AH19" s="54"/>
-      <c r="AI19" s="54"/>
-      <c r="AJ19" s="54"/>
-      <c r="AK19" s="54"/>
-      <c r="AL19" s="54"/>
-      <c r="AM19" s="54"/>
-      <c r="AN19" s="54"/>
-      <c r="AO19" s="54"/>
-      <c r="AP19" s="54"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="54"/>
-      <c r="AS19" s="54"/>
-      <c r="AT19" s="54"/>
-      <c r="AU19" s="54"/>
-      <c r="AV19" s="54"/>
-      <c r="AW19" s="54"/>
-      <c r="AX19" s="54"/>
-      <c r="AY19" s="54"/>
-      <c r="AZ19" s="54"/>
-      <c r="BA19" s="54"/>
-      <c r="BB19" s="54"/>
-      <c r="BC19" s="54"/>
-      <c r="BD19" s="54"/>
-      <c r="BE19" s="54"/>
-      <c r="BF19" s="54"/>
-      <c r="BG19" s="54"/>
-      <c r="BH19" s="54"/>
-      <c r="BI19" s="54"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
+      <c r="AM19" s="57"/>
+      <c r="AN19" s="57"/>
+      <c r="AO19" s="57"/>
+      <c r="AP19" s="57"/>
+      <c r="AQ19" s="57"/>
+      <c r="AR19" s="57"/>
+      <c r="AS19" s="57"/>
+      <c r="AT19" s="57"/>
+      <c r="AU19" s="57"/>
+      <c r="AV19" s="57"/>
+      <c r="AW19" s="57"/>
+      <c r="AX19" s="57"/>
+      <c r="AY19" s="57"/>
+      <c r="AZ19" s="57"/>
+      <c r="BA19" s="57"/>
+      <c r="BB19" s="57"/>
+      <c r="BC19" s="57"/>
+      <c r="BD19" s="57"/>
+      <c r="BE19" s="57"/>
+      <c r="BF19" s="57"/>
+      <c r="BG19" s="57"/>
+      <c r="BH19" s="57"/>
+      <c r="BI19" s="57"/>
     </row>
     <row r="20" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="54"/>
-      <c r="X20" s="54"/>
-      <c r="Y20" s="54"/>
-      <c r="Z20" s="54"/>
-      <c r="AA20" s="54"/>
-      <c r="AB20" s="54"/>
-      <c r="AC20" s="54"/>
-      <c r="AD20" s="54"/>
-      <c r="AE20" s="54"/>
-      <c r="AF20" s="54"/>
-      <c r="AG20" s="54"/>
-      <c r="AH20" s="54"/>
-      <c r="AI20" s="54"/>
-      <c r="AJ20" s="54"/>
-      <c r="AK20" s="54"/>
-      <c r="AL20" s="54"/>
-      <c r="AM20" s="54"/>
-      <c r="AN20" s="54"/>
-      <c r="AO20" s="54"/>
-      <c r="AP20" s="54"/>
-      <c r="AQ20" s="54"/>
-      <c r="AR20" s="54"/>
-      <c r="AS20" s="54"/>
-      <c r="AT20" s="54"/>
-      <c r="AU20" s="54"/>
-      <c r="AV20" s="54"/>
-      <c r="AW20" s="54"/>
-      <c r="AX20" s="54"/>
-      <c r="AY20" s="54"/>
-      <c r="AZ20" s="54"/>
-      <c r="BA20" s="54"/>
-      <c r="BB20" s="54"/>
-      <c r="BC20" s="54"/>
-      <c r="BD20" s="54"/>
-      <c r="BE20" s="54"/>
-      <c r="BF20" s="54"/>
-      <c r="BG20" s="54"/>
-      <c r="BH20" s="54"/>
-      <c r="BI20" s="54"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
+      <c r="Y20" s="57"/>
+      <c r="Z20" s="57"/>
+      <c r="AA20" s="57"/>
+      <c r="AB20" s="57"/>
+      <c r="AC20" s="57"/>
+      <c r="AD20" s="57"/>
+      <c r="AE20" s="57"/>
+      <c r="AF20" s="57"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="57"/>
+      <c r="AI20" s="57"/>
+      <c r="AJ20" s="57"/>
+      <c r="AK20" s="57"/>
+      <c r="AL20" s="57"/>
+      <c r="AM20" s="57"/>
+      <c r="AN20" s="57"/>
+      <c r="AO20" s="57"/>
+      <c r="AP20" s="57"/>
+      <c r="AQ20" s="57"/>
+      <c r="AR20" s="57"/>
+      <c r="AS20" s="57"/>
+      <c r="AT20" s="57"/>
+      <c r="AU20" s="57"/>
+      <c r="AV20" s="57"/>
+      <c r="AW20" s="57"/>
+      <c r="AX20" s="57"/>
+      <c r="AY20" s="57"/>
+      <c r="AZ20" s="57"/>
+      <c r="BA20" s="57"/>
+      <c r="BB20" s="57"/>
+      <c r="BC20" s="57"/>
+      <c r="BD20" s="57"/>
+      <c r="BE20" s="57"/>
+      <c r="BF20" s="57"/>
+      <c r="BG20" s="57"/>
+      <c r="BH20" s="57"/>
+      <c r="BI20" s="57"/>
     </row>
     <row r="21" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-      <c r="X21" s="54"/>
-      <c r="Y21" s="54"/>
-      <c r="Z21" s="54"/>
-      <c r="AA21" s="54"/>
-      <c r="AB21" s="54"/>
-      <c r="AC21" s="54"/>
-      <c r="AD21" s="54"/>
-      <c r="AE21" s="54"/>
-      <c r="AF21" s="54"/>
-      <c r="AG21" s="54"/>
-      <c r="AH21" s="54"/>
-      <c r="AI21" s="54"/>
-      <c r="AJ21" s="54"/>
-      <c r="AK21" s="54"/>
-      <c r="AL21" s="54"/>
-      <c r="AM21" s="54"/>
-      <c r="AN21" s="54"/>
-      <c r="AO21" s="54"/>
-      <c r="AP21" s="54"/>
-      <c r="AQ21" s="54"/>
-      <c r="AR21" s="54"/>
-      <c r="AS21" s="54"/>
-      <c r="AT21" s="54"/>
-      <c r="AU21" s="54"/>
-      <c r="AV21" s="54"/>
-      <c r="AW21" s="54"/>
-      <c r="AX21" s="54"/>
-      <c r="AY21" s="54"/>
-      <c r="AZ21" s="54"/>
-      <c r="BA21" s="54"/>
-      <c r="BB21" s="54"/>
-      <c r="BC21" s="54"/>
-      <c r="BD21" s="54"/>
-      <c r="BE21" s="54"/>
-      <c r="BF21" s="54"/>
-      <c r="BG21" s="54"/>
-      <c r="BH21" s="54"/>
-      <c r="BI21" s="54"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="57"/>
+      <c r="Y21" s="57"/>
+      <c r="Z21" s="57"/>
+      <c r="AA21" s="57"/>
+      <c r="AB21" s="57"/>
+      <c r="AC21" s="57"/>
+      <c r="AD21" s="57"/>
+      <c r="AE21" s="57"/>
+      <c r="AF21" s="57"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="57"/>
+      <c r="AI21" s="57"/>
+      <c r="AJ21" s="57"/>
+      <c r="AK21" s="57"/>
+      <c r="AL21" s="57"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="57"/>
+      <c r="AO21" s="57"/>
+      <c r="AP21" s="57"/>
+      <c r="AQ21" s="57"/>
+      <c r="AR21" s="57"/>
+      <c r="AS21" s="57"/>
+      <c r="AT21" s="57"/>
+      <c r="AU21" s="57"/>
+      <c r="AV21" s="57"/>
+      <c r="AW21" s="57"/>
+      <c r="AX21" s="57"/>
+      <c r="AY21" s="57"/>
+      <c r="AZ21" s="57"/>
+      <c r="BA21" s="57"/>
+      <c r="BB21" s="57"/>
+      <c r="BC21" s="57"/>
+      <c r="BD21" s="57"/>
+      <c r="BE21" s="57"/>
+      <c r="BF21" s="57"/>
+      <c r="BG21" s="57"/>
+      <c r="BH21" s="57"/>
+      <c r="BI21" s="57"/>
     </row>
     <row r="22" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="54"/>
-      <c r="Y22" s="54"/>
-      <c r="Z22" s="54"/>
-      <c r="AA22" s="54"/>
-      <c r="AB22" s="54"/>
-      <c r="AC22" s="54"/>
-      <c r="AD22" s="54"/>
-      <c r="AE22" s="54"/>
-      <c r="AF22" s="54"/>
-      <c r="AG22" s="54"/>
-      <c r="AH22" s="54"/>
-      <c r="AI22" s="54"/>
-      <c r="AJ22" s="54"/>
-      <c r="AK22" s="54"/>
-      <c r="AL22" s="54"/>
-      <c r="AM22" s="54"/>
-      <c r="AN22" s="54"/>
-      <c r="AO22" s="54"/>
-      <c r="AP22" s="54"/>
-      <c r="AQ22" s="54"/>
-      <c r="AR22" s="54"/>
-      <c r="AS22" s="54"/>
-      <c r="AT22" s="54"/>
-      <c r="AU22" s="54"/>
-      <c r="AV22" s="54"/>
-      <c r="AW22" s="54"/>
-      <c r="AX22" s="54"/>
-      <c r="AY22" s="54"/>
-      <c r="AZ22" s="54"/>
-      <c r="BA22" s="54"/>
-      <c r="BB22" s="54"/>
-      <c r="BC22" s="54"/>
-      <c r="BD22" s="54"/>
-      <c r="BE22" s="54"/>
-      <c r="BF22" s="54"/>
-      <c r="BG22" s="54"/>
-      <c r="BH22" s="54"/>
-      <c r="BI22" s="54"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="57"/>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="57"/>
+      <c r="AJ22" s="57"/>
+      <c r="AK22" s="57"/>
+      <c r="AL22" s="57"/>
+      <c r="AM22" s="57"/>
+      <c r="AN22" s="57"/>
+      <c r="AO22" s="57"/>
+      <c r="AP22" s="57"/>
+      <c r="AQ22" s="57"/>
+      <c r="AR22" s="57"/>
+      <c r="AS22" s="57"/>
+      <c r="AT22" s="57"/>
+      <c r="AU22" s="57"/>
+      <c r="AV22" s="57"/>
+      <c r="AW22" s="57"/>
+      <c r="AX22" s="57"/>
+      <c r="AY22" s="57"/>
+      <c r="AZ22" s="57"/>
+      <c r="BA22" s="57"/>
+      <c r="BB22" s="57"/>
+      <c r="BC22" s="57"/>
+      <c r="BD22" s="57"/>
+      <c r="BE22" s="57"/>
+      <c r="BF22" s="57"/>
+      <c r="BG22" s="57"/>
+      <c r="BH22" s="57"/>
+      <c r="BI22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AO12:BI12"/>
+    <mergeCell ref="A17:BI22"/>
+    <mergeCell ref="A16:BI16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="U14:AD14"/>
+    <mergeCell ref="AE14:AN14"/>
+    <mergeCell ref="AO14:BI14"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="U13:AD13"/>
+    <mergeCell ref="AE13:AN13"/>
+    <mergeCell ref="AO13:BI13"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="K12:T12"/>
+    <mergeCell ref="U12:AD12"/>
+    <mergeCell ref="AE12:AN12"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:AC6"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="AJ6:BI6"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="K9:T9"/>
@@ -3128,46 +3162,12 @@
     <mergeCell ref="AE2:AP2"/>
     <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:AC6"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="AJ6:BI6"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="K13:T13"/>
-    <mergeCell ref="U13:AD13"/>
-    <mergeCell ref="AE13:AN13"/>
-    <mergeCell ref="AO13:BI13"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="K12:T12"/>
-    <mergeCell ref="U12:AD12"/>
-    <mergeCell ref="AE12:AN12"/>
-    <mergeCell ref="AO12:BI12"/>
-    <mergeCell ref="A17:BI22"/>
-    <mergeCell ref="A16:BI16"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="K14:T14"/>
-    <mergeCell ref="U14:AD14"/>
-    <mergeCell ref="AE14:AN14"/>
-    <mergeCell ref="AO14:BI14"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3200,71 +3200,71 @@
       <c r="J1" s="58"/>
       <c r="K1" s="58"/>
       <c r="L1" s="58"/>
-      <c r="M1" s="60" t="s">
+      <c r="M1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="59" t="s">
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="60" t="s">
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="59" t="s">
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="59"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="60" t="s">
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="59" t="s">
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54"/>
+      <c r="AT1" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="59"/>
-      <c r="AX1" s="59"/>
-      <c r="AY1" s="59"/>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="60" t="s">
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="57">
+      <c r="BB1" s="54"/>
+      <c r="BC1" s="54"/>
+      <c r="BD1" s="56">
         <v>45554</v>
       </c>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
+      <c r="BE1" s="56"/>
+      <c r="BF1" s="56"/>
+      <c r="BG1" s="56"/>
+      <c r="BH1" s="56"/>
+      <c r="BI1" s="56"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3476,66 +3476,66 @@
       <c r="J2" s="58"/>
       <c r="K2" s="58"/>
       <c r="L2" s="58"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="60" t="s">
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="59" t="str">
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55" t="str">
         <f>クラス仕様!G5</f>
         <v>MainServlet</v>
       </c>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="60" t="s">
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="60" t="s">
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="57"/>
-      <c r="BI2" s="57"/>
+      <c r="BB2" s="54"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="56"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="56"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3735,71 +3735,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="55" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="55"/>
-      <c r="AJ4" s="55"/>
-      <c r="AK4" s="55"/>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="55"/>
-      <c r="AN4" s="55"/>
-      <c r="AO4" s="55"/>
-      <c r="AP4" s="55"/>
-      <c r="AQ4" s="55"/>
-      <c r="AR4" s="55"/>
-      <c r="AS4" s="55"/>
-      <c r="AT4" s="55"/>
-      <c r="AU4" s="55"/>
-      <c r="AV4" s="55"/>
-      <c r="AW4" s="55"/>
-      <c r="AX4" s="55"/>
-      <c r="AY4" s="55"/>
-      <c r="AZ4" s="55"/>
-      <c r="BA4" s="55"/>
-      <c r="BB4" s="55"/>
-      <c r="BC4" s="55"/>
-      <c r="BD4" s="55"/>
-      <c r="BE4" s="55"/>
-      <c r="BF4" s="55"/>
-      <c r="BG4" s="55"/>
-      <c r="BH4" s="55"/>
-      <c r="BI4" s="55"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="61"/>
+      <c r="Z4" s="61"/>
+      <c r="AA4" s="61"/>
+      <c r="AB4" s="61"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61"/>
+      <c r="AM4" s="61"/>
+      <c r="AN4" s="61"/>
+      <c r="AO4" s="61"/>
+      <c r="AP4" s="61"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="61"/>
+      <c r="AT4" s="61"/>
+      <c r="AU4" s="61"/>
+      <c r="AV4" s="61"/>
+      <c r="AW4" s="61"/>
+      <c r="AX4" s="61"/>
+      <c r="AY4" s="61"/>
+      <c r="AZ4" s="61"/>
+      <c r="BA4" s="61"/>
+      <c r="BB4" s="61"/>
+      <c r="BC4" s="61"/>
+      <c r="BD4" s="61"/>
+      <c r="BE4" s="61"/>
+      <c r="BF4" s="61"/>
+      <c r="BG4" s="61"/>
+      <c r="BH4" s="61"/>
+      <c r="BI4" s="61"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3999,71 +3999,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="55"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="55"/>
-      <c r="AH5" s="55"/>
-      <c r="AI5" s="55"/>
-      <c r="AJ5" s="55"/>
-      <c r="AK5" s="55"/>
-      <c r="AL5" s="55"/>
-      <c r="AM5" s="55"/>
-      <c r="AN5" s="55"/>
-      <c r="AO5" s="55"/>
-      <c r="AP5" s="55"/>
-      <c r="AQ5" s="55"/>
-      <c r="AR5" s="55"/>
-      <c r="AS5" s="55"/>
-      <c r="AT5" s="55"/>
-      <c r="AU5" s="55"/>
-      <c r="AV5" s="55"/>
-      <c r="AW5" s="55"/>
-      <c r="AX5" s="55"/>
-      <c r="AY5" s="55"/>
-      <c r="AZ5" s="55"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="55"/>
-      <c r="BC5" s="55"/>
-      <c r="BD5" s="55"/>
-      <c r="BE5" s="55"/>
-      <c r="BF5" s="55"/>
-      <c r="BG5" s="55"/>
-      <c r="BH5" s="55"/>
-      <c r="BI5" s="55"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="61"/>
+      <c r="AB5" s="61"/>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="61"/>
+      <c r="AS5" s="61"/>
+      <c r="AT5" s="61"/>
+      <c r="AU5" s="61"/>
+      <c r="AV5" s="61"/>
+      <c r="AW5" s="61"/>
+      <c r="AX5" s="61"/>
+      <c r="AY5" s="61"/>
+      <c r="AZ5" s="61"/>
+      <c r="BA5" s="61"/>
+      <c r="BB5" s="61"/>
+      <c r="BC5" s="61"/>
+      <c r="BD5" s="61"/>
+      <c r="BE5" s="61"/>
+      <c r="BF5" s="61"/>
+      <c r="BG5" s="61"/>
+      <c r="BH5" s="61"/>
+      <c r="BI5" s="61"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4523,75 +4523,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64" t="s">
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="64"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="64"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-      <c r="AD7" s="64"/>
-      <c r="AE7" s="64" t="s">
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="64"/>
-      <c r="AH7" s="64"/>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="64"/>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="64"/>
-      <c r="AP7" s="64"/>
-      <c r="AQ7" s="64"/>
-      <c r="AR7" s="64"/>
-      <c r="AS7" s="64"/>
-      <c r="AT7" s="64"/>
-      <c r="AU7" s="64"/>
-      <c r="AV7" s="64"/>
-      <c r="AW7" s="64"/>
-      <c r="AX7" s="64"/>
-      <c r="AY7" s="64"/>
-      <c r="AZ7" s="64"/>
-      <c r="BA7" s="64"/>
-      <c r="BB7" s="64"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-      <c r="BE7" s="64"/>
-      <c r="BF7" s="64"/>
-      <c r="BG7" s="64"/>
-      <c r="BH7" s="64"/>
-      <c r="BI7" s="64"/>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="75"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
+      <c r="AL7" s="75"/>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="75"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="75"/>
+      <c r="AZ7" s="75"/>
+      <c r="BA7" s="75"/>
+      <c r="BB7" s="75"/>
+      <c r="BC7" s="75"/>
+      <c r="BD7" s="75"/>
+      <c r="BE7" s="75"/>
+      <c r="BF7" s="75"/>
+      <c r="BG7" s="75"/>
+      <c r="BH7" s="75"/>
+      <c r="BI7" s="75"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4791,75 +4791,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63" t="s">
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="63"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="63"/>
-      <c r="AA8" s="63"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="63"/>
-      <c r="AE8" s="63" t="s">
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="62"/>
+      <c r="AB8" s="62"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="62"/>
+      <c r="AE8" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="AF8" s="63"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="63"/>
-      <c r="AL8" s="63"/>
-      <c r="AM8" s="63"/>
-      <c r="AN8" s="63"/>
-      <c r="AO8" s="63"/>
-      <c r="AP8" s="63"/>
-      <c r="AQ8" s="63"/>
-      <c r="AR8" s="63"/>
-      <c r="AS8" s="63"/>
-      <c r="AT8" s="63"/>
-      <c r="AU8" s="63"/>
-      <c r="AV8" s="63"/>
-      <c r="AW8" s="63"/>
-      <c r="AX8" s="63"/>
-      <c r="AY8" s="63"/>
-      <c r="AZ8" s="63"/>
-      <c r="BA8" s="63"/>
-      <c r="BB8" s="63"/>
-      <c r="BC8" s="63"/>
-      <c r="BD8" s="63"/>
-      <c r="BE8" s="63"/>
-      <c r="BF8" s="63"/>
-      <c r="BG8" s="63"/>
-      <c r="BH8" s="63"/>
-      <c r="BI8" s="63"/>
+      <c r="AF8" s="62"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
+      <c r="AL8" s="62"/>
+      <c r="AM8" s="62"/>
+      <c r="AN8" s="62"/>
+      <c r="AO8" s="62"/>
+      <c r="AP8" s="62"/>
+      <c r="AQ8" s="62"/>
+      <c r="AR8" s="62"/>
+      <c r="AS8" s="62"/>
+      <c r="AT8" s="62"/>
+      <c r="AU8" s="62"/>
+      <c r="AV8" s="62"/>
+      <c r="AW8" s="62"/>
+      <c r="AX8" s="62"/>
+      <c r="AY8" s="62"/>
+      <c r="AZ8" s="62"/>
+      <c r="BA8" s="62"/>
+      <c r="BB8" s="62"/>
+      <c r="BC8" s="62"/>
+      <c r="BD8" s="62"/>
+      <c r="BE8" s="62"/>
+      <c r="BF8" s="62"/>
+      <c r="BG8" s="62"/>
+      <c r="BH8" s="62"/>
+      <c r="BI8" s="62"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -5059,75 +5059,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="63" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63" t="s">
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="63"/>
-      <c r="X9" s="63"/>
-      <c r="Y9" s="63"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="63"/>
-      <c r="AC9" s="63"/>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="63" t="s">
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="62"/>
+      <c r="AC9" s="62"/>
+      <c r="AD9" s="62"/>
+      <c r="AE9" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="AF9" s="63"/>
-      <c r="AG9" s="63"/>
-      <c r="AH9" s="63"/>
-      <c r="AI9" s="63"/>
-      <c r="AJ9" s="63"/>
-      <c r="AK9" s="63"/>
-      <c r="AL9" s="63"/>
-      <c r="AM9" s="63"/>
-      <c r="AN9" s="63"/>
-      <c r="AO9" s="63"/>
-      <c r="AP9" s="63"/>
-      <c r="AQ9" s="63"/>
-      <c r="AR9" s="63"/>
-      <c r="AS9" s="63"/>
-      <c r="AT9" s="63"/>
-      <c r="AU9" s="63"/>
-      <c r="AV9" s="63"/>
-      <c r="AW9" s="63"/>
-      <c r="AX9" s="63"/>
-      <c r="AY9" s="63"/>
-      <c r="AZ9" s="63"/>
-      <c r="BA9" s="63"/>
-      <c r="BB9" s="63"/>
-      <c r="BC9" s="63"/>
-      <c r="BD9" s="63"/>
-      <c r="BE9" s="63"/>
-      <c r="BF9" s="63"/>
-      <c r="BG9" s="63"/>
-      <c r="BH9" s="63"/>
-      <c r="BI9" s="63"/>
+      <c r="AF9" s="62"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="62"/>
+      <c r="AL9" s="62"/>
+      <c r="AM9" s="62"/>
+      <c r="AN9" s="62"/>
+      <c r="AO9" s="62"/>
+      <c r="AP9" s="62"/>
+      <c r="AQ9" s="62"/>
+      <c r="AR9" s="62"/>
+      <c r="AS9" s="62"/>
+      <c r="AT9" s="62"/>
+      <c r="AU9" s="62"/>
+      <c r="AV9" s="62"/>
+      <c r="AW9" s="62"/>
+      <c r="AX9" s="62"/>
+      <c r="AY9" s="62"/>
+      <c r="AZ9" s="62"/>
+      <c r="BA9" s="62"/>
+      <c r="BB9" s="62"/>
+      <c r="BC9" s="62"/>
+      <c r="BD9" s="62"/>
+      <c r="BE9" s="62"/>
+      <c r="BF9" s="62"/>
+      <c r="BG9" s="62"/>
+      <c r="BH9" s="62"/>
+      <c r="BI9" s="62"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5327,75 +5327,75 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="74" t="s">
-        <v>55</v>
+      <c r="A10" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="63" t="s">
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="62"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="62"/>
+      <c r="AA10" s="62"/>
+      <c r="AB10" s="62"/>
+      <c r="AC10" s="62"/>
+      <c r="AD10" s="62"/>
+      <c r="AE10" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63"/>
-      <c r="W10" s="63"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="63"/>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="63"/>
-      <c r="AC10" s="63"/>
-      <c r="AD10" s="63"/>
-      <c r="AE10" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF10" s="63"/>
-      <c r="AG10" s="63"/>
-      <c r="AH10" s="63"/>
-      <c r="AI10" s="63"/>
-      <c r="AJ10" s="63"/>
-      <c r="AK10" s="63"/>
-      <c r="AL10" s="63"/>
-      <c r="AM10" s="63"/>
-      <c r="AN10" s="63"/>
-      <c r="AO10" s="63"/>
-      <c r="AP10" s="63"/>
-      <c r="AQ10" s="63"/>
-      <c r="AR10" s="63"/>
-      <c r="AS10" s="63"/>
-      <c r="AT10" s="63"/>
-      <c r="AU10" s="63"/>
-      <c r="AV10" s="63"/>
-      <c r="AW10" s="63"/>
-      <c r="AX10" s="63"/>
-      <c r="AY10" s="63"/>
-      <c r="AZ10" s="63"/>
-      <c r="BA10" s="63"/>
-      <c r="BB10" s="63"/>
-      <c r="BC10" s="63"/>
-      <c r="BD10" s="63"/>
-      <c r="BE10" s="63"/>
-      <c r="BF10" s="63"/>
-      <c r="BG10" s="63"/>
-      <c r="BH10" s="63"/>
-      <c r="BI10" s="63"/>
+      <c r="AF10" s="62"/>
+      <c r="AG10" s="62"/>
+      <c r="AH10" s="62"/>
+      <c r="AI10" s="62"/>
+      <c r="AJ10" s="62"/>
+      <c r="AK10" s="62"/>
+      <c r="AL10" s="62"/>
+      <c r="AM10" s="62"/>
+      <c r="AN10" s="62"/>
+      <c r="AO10" s="62"/>
+      <c r="AP10" s="62"/>
+      <c r="AQ10" s="62"/>
+      <c r="AR10" s="62"/>
+      <c r="AS10" s="62"/>
+      <c r="AT10" s="62"/>
+      <c r="AU10" s="62"/>
+      <c r="AV10" s="62"/>
+      <c r="AW10" s="62"/>
+      <c r="AX10" s="62"/>
+      <c r="AY10" s="62"/>
+      <c r="AZ10" s="62"/>
+      <c r="BA10" s="62"/>
+      <c r="BB10" s="62"/>
+      <c r="BC10" s="62"/>
+      <c r="BD10" s="62"/>
+      <c r="BE10" s="62"/>
+      <c r="BF10" s="62"/>
+      <c r="BG10" s="62"/>
+      <c r="BH10" s="62"/>
+      <c r="BI10" s="62"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5595,75 +5595,75 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="74" t="s">
-        <v>55</v>
+      <c r="A11" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="63" t="s">
-        <v>62</v>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="62" t="s">
+        <v>60</v>
       </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63" t="s">
-        <v>70</v>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62" t="s">
+        <v>68</v>
       </c>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AC11" s="63"/>
-      <c r="AD11" s="63"/>
-      <c r="AE11" s="63" t="s">
-        <v>78</v>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="62"/>
+      <c r="Z11" s="62"/>
+      <c r="AA11" s="62"/>
+      <c r="AB11" s="62"/>
+      <c r="AC11" s="62"/>
+      <c r="AD11" s="62"/>
+      <c r="AE11" s="62" t="s">
+        <v>76</v>
       </c>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="63"/>
-      <c r="AH11" s="63"/>
-      <c r="AI11" s="63"/>
-      <c r="AJ11" s="63"/>
-      <c r="AK11" s="63"/>
-      <c r="AL11" s="63"/>
-      <c r="AM11" s="63"/>
-      <c r="AN11" s="63"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="63"/>
-      <c r="AR11" s="63"/>
-      <c r="AS11" s="63"/>
-      <c r="AT11" s="63"/>
-      <c r="AU11" s="63"/>
-      <c r="AV11" s="63"/>
-      <c r="AW11" s="63"/>
-      <c r="AX11" s="63"/>
-      <c r="AY11" s="63"/>
-      <c r="AZ11" s="63"/>
-      <c r="BA11" s="63"/>
-      <c r="BB11" s="63"/>
-      <c r="BC11" s="63"/>
-      <c r="BD11" s="63"/>
-      <c r="BE11" s="63"/>
-      <c r="BF11" s="63"/>
-      <c r="BG11" s="63"/>
-      <c r="BH11" s="63"/>
-      <c r="BI11" s="63"/>
+      <c r="AF11" s="62"/>
+      <c r="AG11" s="62"/>
+      <c r="AH11" s="62"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="62"/>
+      <c r="AL11" s="62"/>
+      <c r="AM11" s="62"/>
+      <c r="AN11" s="62"/>
+      <c r="AO11" s="62"/>
+      <c r="AP11" s="62"/>
+      <c r="AQ11" s="62"/>
+      <c r="AR11" s="62"/>
+      <c r="AS11" s="62"/>
+      <c r="AT11" s="62"/>
+      <c r="AU11" s="62"/>
+      <c r="AV11" s="62"/>
+      <c r="AW11" s="62"/>
+      <c r="AX11" s="62"/>
+      <c r="AY11" s="62"/>
+      <c r="AZ11" s="62"/>
+      <c r="BA11" s="62"/>
+      <c r="BB11" s="62"/>
+      <c r="BC11" s="62"/>
+      <c r="BD11" s="62"/>
+      <c r="BE11" s="62"/>
+      <c r="BF11" s="62"/>
+      <c r="BG11" s="62"/>
+      <c r="BH11" s="62"/>
+      <c r="BI11" s="62"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -5863,75 +5863,75 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="74" t="s">
-        <v>55</v>
+      <c r="A12" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="63" t="s">
-        <v>63</v>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="62" t="s">
+        <v>61</v>
       </c>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="63"/>
-      <c r="P12" s="63" t="s">
-        <v>71</v>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62" t="s">
+        <v>69</v>
       </c>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="63"/>
-      <c r="T12" s="63"/>
-      <c r="U12" s="63"/>
-      <c r="V12" s="63"/>
-      <c r="W12" s="63"/>
-      <c r="X12" s="63"/>
-      <c r="Y12" s="63"/>
-      <c r="Z12" s="63"/>
-      <c r="AA12" s="63"/>
-      <c r="AB12" s="63"/>
-      <c r="AC12" s="63"/>
-      <c r="AD12" s="63"/>
-      <c r="AE12" s="63" t="s">
-        <v>79</v>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="62"/>
+      <c r="W12" s="62"/>
+      <c r="X12" s="62"/>
+      <c r="Y12" s="62"/>
+      <c r="Z12" s="62"/>
+      <c r="AA12" s="62"/>
+      <c r="AB12" s="62"/>
+      <c r="AC12" s="62"/>
+      <c r="AD12" s="62"/>
+      <c r="AE12" s="62" t="s">
+        <v>77</v>
       </c>
-      <c r="AF12" s="63"/>
-      <c r="AG12" s="63"/>
-      <c r="AH12" s="63"/>
-      <c r="AI12" s="63"/>
-      <c r="AJ12" s="63"/>
-      <c r="AK12" s="63"/>
-      <c r="AL12" s="63"/>
-      <c r="AM12" s="63"/>
-      <c r="AN12" s="63"/>
-      <c r="AO12" s="63"/>
-      <c r="AP12" s="63"/>
-      <c r="AQ12" s="63"/>
-      <c r="AR12" s="63"/>
-      <c r="AS12" s="63"/>
-      <c r="AT12" s="63"/>
-      <c r="AU12" s="63"/>
-      <c r="AV12" s="63"/>
-      <c r="AW12" s="63"/>
-      <c r="AX12" s="63"/>
-      <c r="AY12" s="63"/>
-      <c r="AZ12" s="63"/>
-      <c r="BA12" s="63"/>
-      <c r="BB12" s="63"/>
-      <c r="BC12" s="63"/>
-      <c r="BD12" s="63"/>
-      <c r="BE12" s="63"/>
-      <c r="BF12" s="63"/>
-      <c r="BG12" s="63"/>
-      <c r="BH12" s="63"/>
-      <c r="BI12" s="63"/>
+      <c r="AF12" s="62"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="62"/>
+      <c r="AL12" s="62"/>
+      <c r="AM12" s="62"/>
+      <c r="AN12" s="62"/>
+      <c r="AO12" s="62"/>
+      <c r="AP12" s="62"/>
+      <c r="AQ12" s="62"/>
+      <c r="AR12" s="62"/>
+      <c r="AS12" s="62"/>
+      <c r="AT12" s="62"/>
+      <c r="AU12" s="62"/>
+      <c r="AV12" s="62"/>
+      <c r="AW12" s="62"/>
+      <c r="AX12" s="62"/>
+      <c r="AY12" s="62"/>
+      <c r="AZ12" s="62"/>
+      <c r="BA12" s="62"/>
+      <c r="BB12" s="62"/>
+      <c r="BC12" s="62"/>
+      <c r="BD12" s="62"/>
+      <c r="BE12" s="62"/>
+      <c r="BF12" s="62"/>
+      <c r="BG12" s="62"/>
+      <c r="BH12" s="62"/>
+      <c r="BI12" s="62"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -6131,75 +6131,75 @@
       <c r="IX12" s="1"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="74" t="s">
-        <v>55</v>
+      <c r="A13" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="63" t="s">
-        <v>68</v>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="62" t="s">
+        <v>66</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="63" t="s">
-        <v>69</v>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62" t="s">
+        <v>67</v>
       </c>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="63"/>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="63"/>
-      <c r="Z13" s="63"/>
-      <c r="AA13" s="63"/>
-      <c r="AB13" s="63"/>
-      <c r="AC13" s="63"/>
-      <c r="AD13" s="63"/>
-      <c r="AE13" s="63" t="s">
-        <v>80</v>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="62"/>
+      <c r="W13" s="62"/>
+      <c r="X13" s="62"/>
+      <c r="Y13" s="62"/>
+      <c r="Z13" s="62"/>
+      <c r="AA13" s="62"/>
+      <c r="AB13" s="62"/>
+      <c r="AC13" s="62"/>
+      <c r="AD13" s="62"/>
+      <c r="AE13" s="62" t="s">
+        <v>78</v>
       </c>
-      <c r="AF13" s="63"/>
-      <c r="AG13" s="63"/>
-      <c r="AH13" s="63"/>
-      <c r="AI13" s="63"/>
-      <c r="AJ13" s="63"/>
-      <c r="AK13" s="63"/>
-      <c r="AL13" s="63"/>
-      <c r="AM13" s="63"/>
-      <c r="AN13" s="63"/>
-      <c r="AO13" s="63"/>
-      <c r="AP13" s="63"/>
-      <c r="AQ13" s="63"/>
-      <c r="AR13" s="63"/>
-      <c r="AS13" s="63"/>
-      <c r="AT13" s="63"/>
-      <c r="AU13" s="63"/>
-      <c r="AV13" s="63"/>
-      <c r="AW13" s="63"/>
-      <c r="AX13" s="63"/>
-      <c r="AY13" s="63"/>
-      <c r="AZ13" s="63"/>
-      <c r="BA13" s="63"/>
-      <c r="BB13" s="63"/>
-      <c r="BC13" s="63"/>
-      <c r="BD13" s="63"/>
-      <c r="BE13" s="63"/>
-      <c r="BF13" s="63"/>
-      <c r="BG13" s="63"/>
-      <c r="BH13" s="63"/>
-      <c r="BI13" s="63"/>
+      <c r="AF13" s="62"/>
+      <c r="AG13" s="62"/>
+      <c r="AH13" s="62"/>
+      <c r="AI13" s="62"/>
+      <c r="AJ13" s="62"/>
+      <c r="AK13" s="62"/>
+      <c r="AL13" s="62"/>
+      <c r="AM13" s="62"/>
+      <c r="AN13" s="62"/>
+      <c r="AO13" s="62"/>
+      <c r="AP13" s="62"/>
+      <c r="AQ13" s="62"/>
+      <c r="AR13" s="62"/>
+      <c r="AS13" s="62"/>
+      <c r="AT13" s="62"/>
+      <c r="AU13" s="62"/>
+      <c r="AV13" s="62"/>
+      <c r="AW13" s="62"/>
+      <c r="AX13" s="62"/>
+      <c r="AY13" s="62"/>
+      <c r="AZ13" s="62"/>
+      <c r="BA13" s="62"/>
+      <c r="BB13" s="62"/>
+      <c r="BC13" s="62"/>
+      <c r="BD13" s="62"/>
+      <c r="BE13" s="62"/>
+      <c r="BF13" s="62"/>
+      <c r="BG13" s="62"/>
+      <c r="BH13" s="62"/>
+      <c r="BI13" s="62"/>
       <c r="BJ13" s="1"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
@@ -6399,75 +6399,75 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63" t="s">
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63" t="s">
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="63"/>
-      <c r="X14" s="63"/>
-      <c r="Y14" s="63"/>
-      <c r="Z14" s="63"/>
-      <c r="AA14" s="63"/>
-      <c r="AB14" s="63"/>
-      <c r="AC14" s="63"/>
-      <c r="AD14" s="63"/>
-      <c r="AE14" s="67" t="s">
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="62"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="62"/>
+      <c r="AB14" s="62"/>
+      <c r="AC14" s="62"/>
+      <c r="AD14" s="62"/>
+      <c r="AE14" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="67"/>
-      <c r="AH14" s="67"/>
-      <c r="AI14" s="67"/>
-      <c r="AJ14" s="67"/>
-      <c r="AK14" s="67"/>
-      <c r="AL14" s="67"/>
-      <c r="AM14" s="67"/>
-      <c r="AN14" s="67"/>
-      <c r="AO14" s="67"/>
-      <c r="AP14" s="67"/>
-      <c r="AQ14" s="67"/>
-      <c r="AR14" s="67"/>
-      <c r="AS14" s="67"/>
-      <c r="AT14" s="67"/>
-      <c r="AU14" s="67"/>
-      <c r="AV14" s="67"/>
-      <c r="AW14" s="67"/>
-      <c r="AX14" s="67"/>
-      <c r="AY14" s="67"/>
-      <c r="AZ14" s="67"/>
-      <c r="BA14" s="67"/>
-      <c r="BB14" s="67"/>
-      <c r="BC14" s="67"/>
-      <c r="BD14" s="67"/>
-      <c r="BE14" s="67"/>
-      <c r="BF14" s="67"/>
-      <c r="BG14" s="67"/>
-      <c r="BH14" s="67"/>
-      <c r="BI14" s="67"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="69"/>
+      <c r="AL14" s="69"/>
+      <c r="AM14" s="69"/>
+      <c r="AN14" s="69"/>
+      <c r="AO14" s="69"/>
+      <c r="AP14" s="69"/>
+      <c r="AQ14" s="69"/>
+      <c r="AR14" s="69"/>
+      <c r="AS14" s="69"/>
+      <c r="AT14" s="69"/>
+      <c r="AU14" s="69"/>
+      <c r="AV14" s="69"/>
+      <c r="AW14" s="69"/>
+      <c r="AX14" s="69"/>
+      <c r="AY14" s="69"/>
+      <c r="AZ14" s="69"/>
+      <c r="BA14" s="69"/>
+      <c r="BB14" s="69"/>
+      <c r="BC14" s="69"/>
+      <c r="BD14" s="69"/>
+      <c r="BE14" s="69"/>
+      <c r="BF14" s="69"/>
+      <c r="BG14" s="69"/>
+      <c r="BH14" s="69"/>
+      <c r="BI14" s="69"/>
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
@@ -6667,75 +6667,75 @@
       <c r="IX14" s="1"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="63"/>
-      <c r="P15" s="63" t="s">
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="Q15" s="63"/>
-      <c r="R15" s="63"/>
-      <c r="S15" s="63"/>
-      <c r="T15" s="63"/>
-      <c r="U15" s="63"/>
-      <c r="V15" s="63"/>
-      <c r="W15" s="63"/>
-      <c r="X15" s="63"/>
-      <c r="Y15" s="63"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="63"/>
-      <c r="AB15" s="63"/>
-      <c r="AC15" s="63"/>
-      <c r="AD15" s="63"/>
-      <c r="AE15" s="63" t="s">
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="62"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="62"/>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="AF15" s="63"/>
-      <c r="AG15" s="63"/>
-      <c r="AH15" s="63"/>
-      <c r="AI15" s="63"/>
-      <c r="AJ15" s="63"/>
-      <c r="AK15" s="63"/>
-      <c r="AL15" s="63"/>
-      <c r="AM15" s="63"/>
-      <c r="AN15" s="63"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="63"/>
-      <c r="AQ15" s="63"/>
-      <c r="AR15" s="63"/>
-      <c r="AS15" s="63"/>
-      <c r="AT15" s="63"/>
-      <c r="AU15" s="63"/>
-      <c r="AV15" s="63"/>
-      <c r="AW15" s="63"/>
-      <c r="AX15" s="63"/>
-      <c r="AY15" s="63"/>
-      <c r="AZ15" s="63"/>
-      <c r="BA15" s="63"/>
-      <c r="BB15" s="63"/>
-      <c r="BC15" s="63"/>
-      <c r="BD15" s="63"/>
-      <c r="BE15" s="63"/>
-      <c r="BF15" s="63"/>
-      <c r="BG15" s="63"/>
-      <c r="BH15" s="63"/>
-      <c r="BI15" s="63"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="62"/>
+      <c r="AM15" s="62"/>
+      <c r="AN15" s="62"/>
+      <c r="AO15" s="62"/>
+      <c r="AP15" s="62"/>
+      <c r="AQ15" s="62"/>
+      <c r="AR15" s="62"/>
+      <c r="AS15" s="62"/>
+      <c r="AT15" s="62"/>
+      <c r="AU15" s="62"/>
+      <c r="AV15" s="62"/>
+      <c r="AW15" s="62"/>
+      <c r="AX15" s="62"/>
+      <c r="AY15" s="62"/>
+      <c r="AZ15" s="62"/>
+      <c r="BA15" s="62"/>
+      <c r="BB15" s="62"/>
+      <c r="BC15" s="62"/>
+      <c r="BD15" s="62"/>
+      <c r="BE15" s="62"/>
+      <c r="BF15" s="62"/>
+      <c r="BG15" s="62"/>
+      <c r="BH15" s="62"/>
+      <c r="BI15" s="62"/>
       <c r="BJ15" s="1"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
@@ -7195,75 +7195,75 @@
       <c r="IX16" s="1"/>
     </row>
     <row r="17" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="71" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="73"/>
-      <c r="S17" s="72" t="s">
+      <c r="P17" s="63"/>
+      <c r="Q17" s="63"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="72"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="72"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
-      <c r="AL17" s="72"/>
-      <c r="AM17" s="72"/>
-      <c r="AN17" s="72"/>
-      <c r="AO17" s="72"/>
-      <c r="AP17" s="72"/>
-      <c r="AQ17" s="72"/>
-      <c r="AR17" s="72"/>
-      <c r="AS17" s="75"/>
-      <c r="AT17" s="65" t="s">
+      <c r="T17" s="63"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="63"/>
+      <c r="W17" s="63"/>
+      <c r="X17" s="63"/>
+      <c r="Y17" s="63"/>
+      <c r="Z17" s="63"/>
+      <c r="AA17" s="63"/>
+      <c r="AB17" s="63"/>
+      <c r="AC17" s="63"/>
+      <c r="AD17" s="63"/>
+      <c r="AE17" s="63"/>
+      <c r="AF17" s="63"/>
+      <c r="AG17" s="63"/>
+      <c r="AH17" s="63"/>
+      <c r="AI17" s="63"/>
+      <c r="AJ17" s="63"/>
+      <c r="AK17" s="63"/>
+      <c r="AL17" s="63"/>
+      <c r="AM17" s="63"/>
+      <c r="AN17" s="63"/>
+      <c r="AO17" s="63"/>
+      <c r="AP17" s="63"/>
+      <c r="AQ17" s="63"/>
+      <c r="AR17" s="63"/>
+      <c r="AS17" s="64"/>
+      <c r="AT17" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="AU17" s="65"/>
-      <c r="AV17" s="65"/>
-      <c r="AW17" s="65"/>
-      <c r="AX17" s="65"/>
-      <c r="AY17" s="65"/>
-      <c r="AZ17" s="65"/>
-      <c r="BA17" s="65"/>
-      <c r="BB17" s="65"/>
-      <c r="BC17" s="65"/>
-      <c r="BD17" s="65"/>
-      <c r="BE17" s="65"/>
-      <c r="BF17" s="65"/>
-      <c r="BG17" s="65"/>
-      <c r="BH17" s="65"/>
-      <c r="BI17" s="66"/>
+      <c r="AU17" s="67"/>
+      <c r="AV17" s="67"/>
+      <c r="AW17" s="67"/>
+      <c r="AX17" s="67"/>
+      <c r="AY17" s="67"/>
+      <c r="AZ17" s="67"/>
+      <c r="BA17" s="67"/>
+      <c r="BB17" s="67"/>
+      <c r="BC17" s="67"/>
+      <c r="BD17" s="67"/>
+      <c r="BE17" s="67"/>
+      <c r="BF17" s="67"/>
+      <c r="BG17" s="67"/>
+      <c r="BH17" s="67"/>
+      <c r="BI17" s="68"/>
       <c r="BJ17" s="1"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="18" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -7486,7 +7486,7 @@
       <c r="Q18" s="45"/>
       <c r="R18" s="43"/>
       <c r="S18" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="AT18" s="7"/>
       <c r="AU18" s="25"/>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="19" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -8248,7 +8248,7 @@
       <c r="Q21" s="45"/>
       <c r="R21" s="43"/>
       <c r="S21" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="22"/>
@@ -8480,7 +8480,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P22" s="52"/>
       <c r="Q22" s="52"/>
@@ -8747,7 +8747,7 @@
       <c r="Q23" s="45"/>
       <c r="R23" s="43"/>
       <c r="S23" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T23" s="21"/>
       <c r="U23" s="12"/>
@@ -9004,7 +9004,7 @@
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
       <c r="O24" s="50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P24" s="45"/>
       <c r="Q24" s="45"/>
@@ -9267,13 +9267,13 @@
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P25" s="45"/>
       <c r="Q25" s="45"/>
       <c r="R25" s="43"/>
       <c r="S25" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T25" s="21"/>
       <c r="U25" s="12"/>
@@ -9531,13 +9531,13 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P26" s="45"/>
       <c r="Q26" s="45"/>
       <c r="R26" s="43"/>
       <c r="S26" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="T26" s="21"/>
       <c r="U26" s="12"/>
@@ -9800,7 +9800,7 @@
       <c r="R27" s="44"/>
       <c r="S27" s="36"/>
       <c r="T27" s="37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U27" s="41"/>
       <c r="V27" s="41"/>
@@ -10063,7 +10063,7 @@
       <c r="Q28" s="46"/>
       <c r="R28" s="43"/>
       <c r="S28" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T28" s="13"/>
       <c r="U28" s="13"/>
@@ -10321,13 +10321,13 @@
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
       <c r="O29" s="51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P29" s="38"/>
       <c r="Q29" s="38"/>
       <c r="R29" s="44"/>
       <c r="S29" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T29" s="38"/>
       <c r="U29" s="38"/>
@@ -10356,7 +10356,7 @@
       <c r="AR29" s="38"/>
       <c r="AS29" s="39"/>
       <c r="AT29" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AU29" s="22"/>
       <c r="AV29" s="22"/>
@@ -10593,7 +10593,7 @@
       <c r="Q30" s="46"/>
       <c r="R30" s="43"/>
       <c r="S30" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AT30" s="7"/>
       <c r="AU30" s="22"/>
@@ -10825,7 +10825,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
       <c r="O31" s="50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P31" s="46"/>
       <c r="Q31" s="46"/>
@@ -11087,7 +11087,7 @@
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
       <c r="O32" s="51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -12321,22 +12321,35 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
-    <mergeCell ref="S17:AS17"/>
-    <mergeCell ref="AE12:BI12"/>
-    <mergeCell ref="D13:O13"/>
-    <mergeCell ref="P13:AD13"/>
-    <mergeCell ref="AE13:BI13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D12:O12"/>
-    <mergeCell ref="P12:AD12"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="BD2:BI2"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="BD1:BI1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:O9"/>
     <mergeCell ref="P9:AD9"/>
@@ -12353,35 +12366,22 @@
     <mergeCell ref="A17:N17"/>
     <mergeCell ref="O17:R17"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="BD2:BI2"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D12:O12"/>
+    <mergeCell ref="P12:AD12"/>
+    <mergeCell ref="S17:AS17"/>
+    <mergeCell ref="AE12:BI12"/>
+    <mergeCell ref="D13:O13"/>
+    <mergeCell ref="P13:AD13"/>
+    <mergeCell ref="AE13:BI13"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="2">
@@ -12422,71 +12422,71 @@
       <c r="J1" s="58"/>
       <c r="K1" s="58"/>
       <c r="L1" s="58"/>
-      <c r="M1" s="60" t="s">
+      <c r="M1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="59" t="s">
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="60" t="s">
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="59" t="s">
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="59"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="60" t="s">
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="59" t="s">
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54"/>
+      <c r="AT1" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="59"/>
-      <c r="AX1" s="59"/>
-      <c r="AY1" s="59"/>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="60" t="s">
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="57">
+      <c r="BB1" s="54"/>
+      <c r="BC1" s="54"/>
+      <c r="BD1" s="56">
         <v>45554</v>
       </c>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="57"/>
-      <c r="BG1" s="57"/>
-      <c r="BH1" s="57"/>
-      <c r="BI1" s="57"/>
+      <c r="BE1" s="56"/>
+      <c r="BF1" s="56"/>
+      <c r="BG1" s="56"/>
+      <c r="BH1" s="56"/>
+      <c r="BI1" s="56"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -12698,66 +12698,66 @@
       <c r="J2" s="58"/>
       <c r="K2" s="58"/>
       <c r="L2" s="58"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="60" t="s">
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="59" t="str">
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55" t="str">
         <f>クラス仕様!G5</f>
         <v>MainServlet</v>
       </c>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="60" t="s">
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="60" t="s">
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="57"/>
-      <c r="BI2" s="57"/>
+      <c r="BB2" s="54"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="56"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="56"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -12957,71 +12957,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="55" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="55"/>
-      <c r="AJ4" s="55"/>
-      <c r="AK4" s="55"/>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="55"/>
-      <c r="AN4" s="55"/>
-      <c r="AO4" s="55"/>
-      <c r="AP4" s="55"/>
-      <c r="AQ4" s="55"/>
-      <c r="AR4" s="55"/>
-      <c r="AS4" s="55"/>
-      <c r="AT4" s="55"/>
-      <c r="AU4" s="55"/>
-      <c r="AV4" s="55"/>
-      <c r="AW4" s="55"/>
-      <c r="AX4" s="55"/>
-      <c r="AY4" s="55"/>
-      <c r="AZ4" s="55"/>
-      <c r="BA4" s="55"/>
-      <c r="BB4" s="55"/>
-      <c r="BC4" s="55"/>
-      <c r="BD4" s="55"/>
-      <c r="BE4" s="55"/>
-      <c r="BF4" s="55"/>
-      <c r="BG4" s="55"/>
-      <c r="BH4" s="55"/>
-      <c r="BI4" s="55"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="61"/>
+      <c r="Z4" s="61"/>
+      <c r="AA4" s="61"/>
+      <c r="AB4" s="61"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61"/>
+      <c r="AM4" s="61"/>
+      <c r="AN4" s="61"/>
+      <c r="AO4" s="61"/>
+      <c r="AP4" s="61"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="61"/>
+      <c r="AT4" s="61"/>
+      <c r="AU4" s="61"/>
+      <c r="AV4" s="61"/>
+      <c r="AW4" s="61"/>
+      <c r="AX4" s="61"/>
+      <c r="AY4" s="61"/>
+      <c r="AZ4" s="61"/>
+      <c r="BA4" s="61"/>
+      <c r="BB4" s="61"/>
+      <c r="BC4" s="61"/>
+      <c r="BD4" s="61"/>
+      <c r="BE4" s="61"/>
+      <c r="BF4" s="61"/>
+      <c r="BG4" s="61"/>
+      <c r="BH4" s="61"/>
+      <c r="BI4" s="61"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -13221,71 +13221,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="55"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="55"/>
-      <c r="AH5" s="55"/>
-      <c r="AI5" s="55"/>
-      <c r="AJ5" s="55"/>
-      <c r="AK5" s="55"/>
-      <c r="AL5" s="55"/>
-      <c r="AM5" s="55"/>
-      <c r="AN5" s="55"/>
-      <c r="AO5" s="55"/>
-      <c r="AP5" s="55"/>
-      <c r="AQ5" s="55"/>
-      <c r="AR5" s="55"/>
-      <c r="AS5" s="55"/>
-      <c r="AT5" s="55"/>
-      <c r="AU5" s="55"/>
-      <c r="AV5" s="55"/>
-      <c r="AW5" s="55"/>
-      <c r="AX5" s="55"/>
-      <c r="AY5" s="55"/>
-      <c r="AZ5" s="55"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="55"/>
-      <c r="BC5" s="55"/>
-      <c r="BD5" s="55"/>
-      <c r="BE5" s="55"/>
-      <c r="BF5" s="55"/>
-      <c r="BG5" s="55"/>
-      <c r="BH5" s="55"/>
-      <c r="BI5" s="55"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="61"/>
+      <c r="AB5" s="61"/>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="61"/>
+      <c r="AS5" s="61"/>
+      <c r="AT5" s="61"/>
+      <c r="AU5" s="61"/>
+      <c r="AV5" s="61"/>
+      <c r="AW5" s="61"/>
+      <c r="AX5" s="61"/>
+      <c r="AY5" s="61"/>
+      <c r="AZ5" s="61"/>
+      <c r="BA5" s="61"/>
+      <c r="BB5" s="61"/>
+      <c r="BC5" s="61"/>
+      <c r="BD5" s="61"/>
+      <c r="BE5" s="61"/>
+      <c r="BF5" s="61"/>
+      <c r="BG5" s="61"/>
+      <c r="BH5" s="61"/>
+      <c r="BI5" s="61"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -13745,75 +13745,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64" t="s">
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="64"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="64"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-      <c r="AD7" s="64"/>
-      <c r="AE7" s="64" t="s">
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="64"/>
-      <c r="AH7" s="64"/>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="64"/>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="64"/>
-      <c r="AP7" s="64"/>
-      <c r="AQ7" s="64"/>
-      <c r="AR7" s="64"/>
-      <c r="AS7" s="64"/>
-      <c r="AT7" s="64"/>
-      <c r="AU7" s="64"/>
-      <c r="AV7" s="64"/>
-      <c r="AW7" s="64"/>
-      <c r="AX7" s="64"/>
-      <c r="AY7" s="64"/>
-      <c r="AZ7" s="64"/>
-      <c r="BA7" s="64"/>
-      <c r="BB7" s="64"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-      <c r="BE7" s="64"/>
-      <c r="BF7" s="64"/>
-      <c r="BG7" s="64"/>
-      <c r="BH7" s="64"/>
-      <c r="BI7" s="64"/>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="75"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
+      <c r="AL7" s="75"/>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="75"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="75"/>
+      <c r="AZ7" s="75"/>
+      <c r="BA7" s="75"/>
+      <c r="BB7" s="75"/>
+      <c r="BC7" s="75"/>
+      <c r="BD7" s="75"/>
+      <c r="BE7" s="75"/>
+      <c r="BF7" s="75"/>
+      <c r="BG7" s="75"/>
+      <c r="BH7" s="75"/>
+      <c r="BI7" s="75"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -14013,75 +14013,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63" t="s">
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="63"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="63"/>
-      <c r="AA8" s="63"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="63"/>
-      <c r="AE8" s="63" t="s">
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="62"/>
+      <c r="AB8" s="62"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="62"/>
+      <c r="AE8" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="AF8" s="63"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="63"/>
-      <c r="AL8" s="63"/>
-      <c r="AM8" s="63"/>
-      <c r="AN8" s="63"/>
-      <c r="AO8" s="63"/>
-      <c r="AP8" s="63"/>
-      <c r="AQ8" s="63"/>
-      <c r="AR8" s="63"/>
-      <c r="AS8" s="63"/>
-      <c r="AT8" s="63"/>
-      <c r="AU8" s="63"/>
-      <c r="AV8" s="63"/>
-      <c r="AW8" s="63"/>
-      <c r="AX8" s="63"/>
-      <c r="AY8" s="63"/>
-      <c r="AZ8" s="63"/>
-      <c r="BA8" s="63"/>
-      <c r="BB8" s="63"/>
-      <c r="BC8" s="63"/>
-      <c r="BD8" s="63"/>
-      <c r="BE8" s="63"/>
-      <c r="BF8" s="63"/>
-      <c r="BG8" s="63"/>
-      <c r="BH8" s="63"/>
-      <c r="BI8" s="63"/>
+      <c r="AF8" s="62"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
+      <c r="AL8" s="62"/>
+      <c r="AM8" s="62"/>
+      <c r="AN8" s="62"/>
+      <c r="AO8" s="62"/>
+      <c r="AP8" s="62"/>
+      <c r="AQ8" s="62"/>
+      <c r="AR8" s="62"/>
+      <c r="AS8" s="62"/>
+      <c r="AT8" s="62"/>
+      <c r="AU8" s="62"/>
+      <c r="AV8" s="62"/>
+      <c r="AW8" s="62"/>
+      <c r="AX8" s="62"/>
+      <c r="AY8" s="62"/>
+      <c r="AZ8" s="62"/>
+      <c r="BA8" s="62"/>
+      <c r="BB8" s="62"/>
+      <c r="BC8" s="62"/>
+      <c r="BD8" s="62"/>
+      <c r="BE8" s="62"/>
+      <c r="BF8" s="62"/>
+      <c r="BG8" s="62"/>
+      <c r="BH8" s="62"/>
+      <c r="BI8" s="62"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -14281,75 +14281,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="63" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63" t="s">
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="63"/>
-      <c r="X9" s="63"/>
-      <c r="Y9" s="63"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="63"/>
-      <c r="AC9" s="63"/>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="63" t="s">
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="62"/>
+      <c r="AC9" s="62"/>
+      <c r="AD9" s="62"/>
+      <c r="AE9" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="AF9" s="63"/>
-      <c r="AG9" s="63"/>
-      <c r="AH9" s="63"/>
-      <c r="AI9" s="63"/>
-      <c r="AJ9" s="63"/>
-      <c r="AK9" s="63"/>
-      <c r="AL9" s="63"/>
-      <c r="AM9" s="63"/>
-      <c r="AN9" s="63"/>
-      <c r="AO9" s="63"/>
-      <c r="AP9" s="63"/>
-      <c r="AQ9" s="63"/>
-      <c r="AR9" s="63"/>
-      <c r="AS9" s="63"/>
-      <c r="AT9" s="63"/>
-      <c r="AU9" s="63"/>
-      <c r="AV9" s="63"/>
-      <c r="AW9" s="63"/>
-      <c r="AX9" s="63"/>
-      <c r="AY9" s="63"/>
-      <c r="AZ9" s="63"/>
-      <c r="BA9" s="63"/>
-      <c r="BB9" s="63"/>
-      <c r="BC9" s="63"/>
-      <c r="BD9" s="63"/>
-      <c r="BE9" s="63"/>
-      <c r="BF9" s="63"/>
-      <c r="BG9" s="63"/>
-      <c r="BH9" s="63"/>
-      <c r="BI9" s="63"/>
+      <c r="AF9" s="62"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="62"/>
+      <c r="AL9" s="62"/>
+      <c r="AM9" s="62"/>
+      <c r="AN9" s="62"/>
+      <c r="AO9" s="62"/>
+      <c r="AP9" s="62"/>
+      <c r="AQ9" s="62"/>
+      <c r="AR9" s="62"/>
+      <c r="AS9" s="62"/>
+      <c r="AT9" s="62"/>
+      <c r="AU9" s="62"/>
+      <c r="AV9" s="62"/>
+      <c r="AW9" s="62"/>
+      <c r="AX9" s="62"/>
+      <c r="AY9" s="62"/>
+      <c r="AZ9" s="62"/>
+      <c r="BA9" s="62"/>
+      <c r="BB9" s="62"/>
+      <c r="BC9" s="62"/>
+      <c r="BD9" s="62"/>
+      <c r="BE9" s="62"/>
+      <c r="BF9" s="62"/>
+      <c r="BG9" s="62"/>
+      <c r="BH9" s="62"/>
+      <c r="BI9" s="62"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -14549,75 +14549,75 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="63" t="s">
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63"/>
-      <c r="W10" s="63"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="63"/>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="63"/>
-      <c r="AC10" s="63"/>
-      <c r="AD10" s="63"/>
-      <c r="AE10" s="67" t="s">
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="62"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="62"/>
+      <c r="AA10" s="62"/>
+      <c r="AB10" s="62"/>
+      <c r="AC10" s="62"/>
+      <c r="AD10" s="62"/>
+      <c r="AE10" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="AF10" s="67"/>
-      <c r="AG10" s="67"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="67"/>
-      <c r="AL10" s="67"/>
-      <c r="AM10" s="67"/>
-      <c r="AN10" s="67"/>
-      <c r="AO10" s="67"/>
-      <c r="AP10" s="67"/>
-      <c r="AQ10" s="67"/>
-      <c r="AR10" s="67"/>
-      <c r="AS10" s="67"/>
-      <c r="AT10" s="67"/>
-      <c r="AU10" s="67"/>
-      <c r="AV10" s="67"/>
-      <c r="AW10" s="67"/>
-      <c r="AX10" s="67"/>
-      <c r="AY10" s="67"/>
-      <c r="AZ10" s="67"/>
-      <c r="BA10" s="67"/>
-      <c r="BB10" s="67"/>
-      <c r="BC10" s="67"/>
-      <c r="BD10" s="67"/>
-      <c r="BE10" s="67"/>
-      <c r="BF10" s="67"/>
-      <c r="BG10" s="67"/>
-      <c r="BH10" s="67"/>
-      <c r="BI10" s="67"/>
+      <c r="AF10" s="69"/>
+      <c r="AG10" s="69"/>
+      <c r="AH10" s="69"/>
+      <c r="AI10" s="69"/>
+      <c r="AJ10" s="69"/>
+      <c r="AK10" s="69"/>
+      <c r="AL10" s="69"/>
+      <c r="AM10" s="69"/>
+      <c r="AN10" s="69"/>
+      <c r="AO10" s="69"/>
+      <c r="AP10" s="69"/>
+      <c r="AQ10" s="69"/>
+      <c r="AR10" s="69"/>
+      <c r="AS10" s="69"/>
+      <c r="AT10" s="69"/>
+      <c r="AU10" s="69"/>
+      <c r="AV10" s="69"/>
+      <c r="AW10" s="69"/>
+      <c r="AX10" s="69"/>
+      <c r="AY10" s="69"/>
+      <c r="AZ10" s="69"/>
+      <c r="BA10" s="69"/>
+      <c r="BB10" s="69"/>
+      <c r="BC10" s="69"/>
+      <c r="BD10" s="69"/>
+      <c r="BE10" s="69"/>
+      <c r="BF10" s="69"/>
+      <c r="BG10" s="69"/>
+      <c r="BH10" s="69"/>
+      <c r="BI10" s="69"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -14817,75 +14817,75 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="63" t="s">
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63" t="s">
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AC11" s="63"/>
-      <c r="AD11" s="63"/>
-      <c r="AE11" s="63" t="s">
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="62"/>
+      <c r="Z11" s="62"/>
+      <c r="AA11" s="62"/>
+      <c r="AB11" s="62"/>
+      <c r="AC11" s="62"/>
+      <c r="AD11" s="62"/>
+      <c r="AE11" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="63"/>
-      <c r="AH11" s="63"/>
-      <c r="AI11" s="63"/>
-      <c r="AJ11" s="63"/>
-      <c r="AK11" s="63"/>
-      <c r="AL11" s="63"/>
-      <c r="AM11" s="63"/>
-      <c r="AN11" s="63"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="63"/>
-      <c r="AR11" s="63"/>
-      <c r="AS11" s="63"/>
-      <c r="AT11" s="63"/>
-      <c r="AU11" s="63"/>
-      <c r="AV11" s="63"/>
-      <c r="AW11" s="63"/>
-      <c r="AX11" s="63"/>
-      <c r="AY11" s="63"/>
-      <c r="AZ11" s="63"/>
-      <c r="BA11" s="63"/>
-      <c r="BB11" s="63"/>
-      <c r="BC11" s="63"/>
-      <c r="BD11" s="63"/>
-      <c r="BE11" s="63"/>
-      <c r="BF11" s="63"/>
-      <c r="BG11" s="63"/>
-      <c r="BH11" s="63"/>
-      <c r="BI11" s="63"/>
+      <c r="AF11" s="62"/>
+      <c r="AG11" s="62"/>
+      <c r="AH11" s="62"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="62"/>
+      <c r="AL11" s="62"/>
+      <c r="AM11" s="62"/>
+      <c r="AN11" s="62"/>
+      <c r="AO11" s="62"/>
+      <c r="AP11" s="62"/>
+      <c r="AQ11" s="62"/>
+      <c r="AR11" s="62"/>
+      <c r="AS11" s="62"/>
+      <c r="AT11" s="62"/>
+      <c r="AU11" s="62"/>
+      <c r="AV11" s="62"/>
+      <c r="AW11" s="62"/>
+      <c r="AX11" s="62"/>
+      <c r="AY11" s="62"/>
+      <c r="AZ11" s="62"/>
+      <c r="BA11" s="62"/>
+      <c r="BB11" s="62"/>
+      <c r="BC11" s="62"/>
+      <c r="BD11" s="62"/>
+      <c r="BE11" s="62"/>
+      <c r="BF11" s="62"/>
+      <c r="BG11" s="62"/>
+      <c r="BH11" s="62"/>
+      <c r="BI11" s="62"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -15345,73 +15345,73 @@
       <c r="IX12" s="1"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="65" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="65"/>
-      <c r="Z13" s="65"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="65"/>
-      <c r="AC13" s="65"/>
-      <c r="AD13" s="65"/>
-      <c r="AE13" s="65"/>
-      <c r="AF13" s="65"/>
-      <c r="AG13" s="65"/>
-      <c r="AH13" s="65"/>
-      <c r="AI13" s="65"/>
-      <c r="AJ13" s="65"/>
-      <c r="AK13" s="65"/>
-      <c r="AL13" s="65"/>
-      <c r="AM13" s="65"/>
-      <c r="AN13" s="65"/>
-      <c r="AO13" s="65"/>
-      <c r="AP13" s="65"/>
-      <c r="AQ13" s="65"/>
-      <c r="AR13" s="65"/>
-      <c r="AS13" s="65"/>
-      <c r="AT13" s="65" t="s">
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+      <c r="U13" s="67"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="67"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="67"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
+      <c r="AK13" s="67"/>
+      <c r="AL13" s="67"/>
+      <c r="AM13" s="67"/>
+      <c r="AN13" s="67"/>
+      <c r="AO13" s="67"/>
+      <c r="AP13" s="67"/>
+      <c r="AQ13" s="67"/>
+      <c r="AR13" s="67"/>
+      <c r="AS13" s="67"/>
+      <c r="AT13" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="AU13" s="65"/>
-      <c r="AV13" s="65"/>
-      <c r="AW13" s="65"/>
-      <c r="AX13" s="65"/>
-      <c r="AY13" s="65"/>
-      <c r="AZ13" s="65"/>
-      <c r="BA13" s="65"/>
-      <c r="BB13" s="65"/>
-      <c r="BC13" s="65"/>
-      <c r="BD13" s="65"/>
-      <c r="BE13" s="65"/>
-      <c r="BF13" s="65"/>
-      <c r="BG13" s="65"/>
-      <c r="BH13" s="65"/>
-      <c r="BI13" s="66"/>
+      <c r="AU13" s="67"/>
+      <c r="AV13" s="67"/>
+      <c r="AW13" s="67"/>
+      <c r="AX13" s="67"/>
+      <c r="AY13" s="67"/>
+      <c r="AZ13" s="67"/>
+      <c r="BA13" s="67"/>
+      <c r="BB13" s="67"/>
+      <c r="BC13" s="67"/>
+      <c r="BD13" s="67"/>
+      <c r="BE13" s="67"/>
+      <c r="BF13" s="67"/>
+      <c r="BG13" s="67"/>
+      <c r="BH13" s="67"/>
+      <c r="BI13" s="68"/>
       <c r="BJ13" s="1"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
@@ -26264,11 +26264,29 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="AT13:BI13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="P13:AS13"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
     <mergeCell ref="A5:F5"/>
@@ -26285,29 +26303,11 @@
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
     <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="AT13:BI13"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
-    <mergeCell ref="P13:AS13"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -26323,18 +26323,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26470,18 +26470,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC473E1-630C-47C0-8277-41F4549C3C72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E88503-2BF5-4213-82B7-01925F2C7A20}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E88503-2BF5-4213-82B7-01925F2C7A20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC473E1-630C-47C0-8277-41F4549C3C72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
